--- a/raw/Timetable_2026Autumn_2025CS.xlsx
+++ b/raw/Timetable_2026Autumn_2025CS.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30502"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D9308CC-50C6-491A-8110-F2AD1E80206A}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{177D202B-8165-4FF7-8D1A-F62E84AFD9D2}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025CS1" sheetId="2" r:id="rId1"/>
@@ -1133,10 +1133,52 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1145,19 +1187,22 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1175,54 +1220,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -1567,81 +1567,81 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="73" t="s">
+      <c r="B2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="74"/>
-      <c r="D2" s="63" t="s">
+      <c r="C2" s="89"/>
+      <c r="D2" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63" t="s">
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="63" t="s">
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="63"/>
-      <c r="L2" s="63"/>
-      <c r="M2" s="63" t="s">
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="63"/>
-      <c r="O2" s="63"/>
-      <c r="P2" s="63" t="s">
+      <c r="N2" s="77"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="63"/>
-      <c r="R2" s="63"/>
-      <c r="S2" s="63" t="s">
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="63"/>
-      <c r="U2" s="63"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
     </row>
     <row r="3" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="72" t="s">
+      <c r="A3" s="77"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="87" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="63" t="s">
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63" t="s">
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="63"/>
-      <c r="L3" s="63"/>
-      <c r="M3" s="63" t="s">
+      <c r="K3" s="77"/>
+      <c r="L3" s="77"/>
+      <c r="M3" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="63"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63" t="s">
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="64">
+      <c r="A4" s="67">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1699,7 +1699,7 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="64"/>
+      <c r="A5" s="67"/>
       <c r="B5" s="2" t="s">
         <v>23</v>
       </c>
@@ -1745,7 +1745,7 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="64"/>
+      <c r="A6" s="67"/>
       <c r="B6" s="2" t="s">
         <v>27</v>
       </c>
@@ -1791,7 +1791,7 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="64"/>
+      <c r="A7" s="67"/>
       <c r="B7" s="2" t="s">
         <v>29</v>
       </c>
@@ -1835,7 +1835,7 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="64"/>
+      <c r="A8" s="67"/>
       <c r="B8" s="2" t="s">
         <v>32</v>
       </c>
@@ -1899,7 +1899,7 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="64"/>
+      <c r="A9" s="67"/>
       <c r="B9" s="2" t="s">
         <v>37</v>
       </c>
@@ -1941,7 +1941,7 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="64"/>
+      <c r="A10" s="67"/>
       <c r="B10" s="2" t="s">
         <v>40</v>
       </c>
@@ -1985,7 +1985,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="71">
+      <c r="A11" s="63">
         <v>2</v>
       </c>
       <c r="B11" s="11" t="s">
@@ -2049,7 +2049,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="71"/>
+      <c r="A12" s="63"/>
       <c r="B12" s="11" t="s">
         <v>46</v>
       </c>
@@ -2111,7 +2111,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="71"/>
+      <c r="A13" s="63"/>
       <c r="B13" s="11" t="s">
         <v>48</v>
       </c>
@@ -2145,7 +2145,7 @@
       <c r="AA13" s="10"/>
     </row>
     <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="71"/>
+      <c r="A14" s="63"/>
       <c r="B14" s="11" t="s">
         <v>49</v>
       </c>
@@ -2209,7 +2209,7 @@
       <c r="AA14" s="10"/>
     </row>
     <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="71"/>
+      <c r="A15" s="63"/>
       <c r="B15" s="11" t="s">
         <v>53</v>
       </c>
@@ -2261,7 +2261,7 @@
       <c r="AA15" s="10"/>
     </row>
     <row r="16" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="71"/>
+      <c r="A16" s="63"/>
       <c r="B16" s="11" t="s">
         <v>54</v>
       </c>
@@ -2288,7 +2288,7 @@
       <c r="U16" s="15"/>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="71"/>
+      <c r="A17" s="63"/>
       <c r="B17" s="11" t="s">
         <v>55</v>
       </c>
@@ -2315,7 +2315,7 @@
       <c r="U17" s="15"/>
     </row>
     <row r="18" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="64">
+      <c r="A18" s="67">
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -2364,7 +2364,7 @@
       <c r="U18" s="6"/>
     </row>
     <row r="19" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="64"/>
+      <c r="A19" s="67"/>
       <c r="B19" s="2" t="s">
         <v>57</v>
       </c>
@@ -2393,7 +2393,7 @@
       <c r="U19" s="6"/>
     </row>
     <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="64"/>
+      <c r="A20" s="67"/>
       <c r="B20" s="2" t="s">
         <v>58</v>
       </c>
@@ -2440,7 +2440,7 @@
       <c r="U20" s="6"/>
     </row>
     <row r="21" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="64"/>
+      <c r="A21" s="67"/>
       <c r="B21" s="2" t="s">
         <v>60</v>
       </c>
@@ -2481,7 +2481,7 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="64"/>
+      <c r="A22" s="67"/>
       <c r="B22" s="2" t="s">
         <v>61</v>
       </c>
@@ -2528,7 +2528,7 @@
       <c r="U22" s="6"/>
     </row>
     <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="64"/>
+      <c r="A23" s="67"/>
       <c r="B23" s="2" t="s">
         <v>62</v>
       </c>
@@ -2555,7 +2555,7 @@
       <c r="U23" s="6"/>
     </row>
     <row r="24" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="64"/>
+      <c r="A24" s="67"/>
       <c r="B24" s="19" t="s">
         <v>63</v>
       </c>
@@ -2600,7 +2600,7 @@
       <c r="U24" s="26"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="71">
+      <c r="A25" s="63">
         <v>4</v>
       </c>
       <c r="B25" s="11" t="s">
@@ -2649,7 +2649,7 @@
       <c r="U25" s="15"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="71"/>
+      <c r="A26" s="63"/>
       <c r="B26" s="11" t="s">
         <v>65</v>
       </c>
@@ -2696,7 +2696,7 @@
       <c r="U26" s="15"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="71"/>
+      <c r="A27" s="63"/>
       <c r="B27" s="11" t="s">
         <v>66</v>
       </c>
@@ -2743,7 +2743,7 @@
       <c r="U27" s="15"/>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="71"/>
+      <c r="A28" s="63"/>
       <c r="B28" s="11" t="s">
         <v>67</v>
       </c>
@@ -2790,90 +2790,90 @@
       <c r="U28" s="15"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="71"/>
+      <c r="A29" s="63"/>
       <c r="B29" s="32" t="s">
         <v>68</v>
       </c>
       <c r="C29" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="D29" s="86" t="s">
+      <c r="D29" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="E29" s="65"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
-      <c r="H29" s="65"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="65"/>
-      <c r="K29" s="65"/>
-      <c r="L29" s="65"/>
-      <c r="M29" s="65"/>
-      <c r="N29" s="65"/>
-      <c r="O29" s="65"/>
-      <c r="P29" s="65"/>
-      <c r="Q29" s="65"/>
-      <c r="R29" s="65"/>
-      <c r="S29" s="65"/>
-      <c r="T29" s="65"/>
-      <c r="U29" s="66"/>
+      <c r="E29" s="79"/>
+      <c r="F29" s="79"/>
+      <c r="G29" s="79"/>
+      <c r="H29" s="79"/>
+      <c r="I29" s="79"/>
+      <c r="J29" s="79"/>
+      <c r="K29" s="79"/>
+      <c r="L29" s="79"/>
+      <c r="M29" s="79"/>
+      <c r="N29" s="79"/>
+      <c r="O29" s="79"/>
+      <c r="P29" s="79"/>
+      <c r="Q29" s="79"/>
+      <c r="R29" s="79"/>
+      <c r="S29" s="79"/>
+      <c r="T29" s="79"/>
+      <c r="U29" s="80"/>
     </row>
     <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="71"/>
+      <c r="A30" s="63"/>
       <c r="B30" s="32" t="s">
         <v>70</v>
       </c>
       <c r="C30" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="D30" s="87"/>
-      <c r="E30" s="67"/>
-      <c r="F30" s="67"/>
-      <c r="G30" s="67"/>
-      <c r="H30" s="67"/>
-      <c r="I30" s="67"/>
-      <c r="J30" s="67"/>
-      <c r="K30" s="67"/>
-      <c r="L30" s="67"/>
-      <c r="M30" s="67"/>
-      <c r="N30" s="67"/>
-      <c r="O30" s="67"/>
-      <c r="P30" s="67"/>
-      <c r="Q30" s="67"/>
-      <c r="R30" s="67"/>
-      <c r="S30" s="67"/>
-      <c r="T30" s="67"/>
-      <c r="U30" s="68"/>
+      <c r="D30" s="81"/>
+      <c r="E30" s="82"/>
+      <c r="F30" s="82"/>
+      <c r="G30" s="82"/>
+      <c r="H30" s="82"/>
+      <c r="I30" s="82"/>
+      <c r="J30" s="82"/>
+      <c r="K30" s="82"/>
+      <c r="L30" s="82"/>
+      <c r="M30" s="82"/>
+      <c r="N30" s="82"/>
+      <c r="O30" s="82"/>
+      <c r="P30" s="82"/>
+      <c r="Q30" s="82"/>
+      <c r="R30" s="82"/>
+      <c r="S30" s="82"/>
+      <c r="T30" s="82"/>
+      <c r="U30" s="83"/>
     </row>
     <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="71"/>
+      <c r="A31" s="63"/>
       <c r="B31" s="32" t="s">
         <v>71</v>
       </c>
       <c r="C31" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="88"/>
-      <c r="E31" s="69"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="69"/>
-      <c r="H31" s="69"/>
-      <c r="I31" s="69"/>
-      <c r="J31" s="69"/>
-      <c r="K31" s="69"/>
-      <c r="L31" s="69"/>
-      <c r="M31" s="69"/>
-      <c r="N31" s="69"/>
-      <c r="O31" s="69"/>
-      <c r="P31" s="69"/>
-      <c r="Q31" s="69"/>
-      <c r="R31" s="69"/>
-      <c r="S31" s="69"/>
-      <c r="T31" s="69"/>
-      <c r="U31" s="70"/>
+      <c r="D31" s="84"/>
+      <c r="E31" s="85"/>
+      <c r="F31" s="85"/>
+      <c r="G31" s="85"/>
+      <c r="H31" s="85"/>
+      <c r="I31" s="85"/>
+      <c r="J31" s="85"/>
+      <c r="K31" s="85"/>
+      <c r="L31" s="85"/>
+      <c r="M31" s="85"/>
+      <c r="N31" s="85"/>
+      <c r="O31" s="85"/>
+      <c r="P31" s="85"/>
+      <c r="Q31" s="85"/>
+      <c r="R31" s="85"/>
+      <c r="S31" s="85"/>
+      <c r="T31" s="85"/>
+      <c r="U31" s="86"/>
     </row>
     <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="64">
+      <c r="A32" s="67">
         <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -2922,7 +2922,7 @@
       <c r="U32" s="6"/>
     </row>
     <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="64"/>
+      <c r="A33" s="67"/>
       <c r="B33" s="2" t="s">
         <v>73</v>
       </c>
@@ -2969,7 +2969,7 @@
       <c r="U33" s="6"/>
     </row>
     <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="64"/>
+      <c r="A34" s="67"/>
       <c r="B34" s="2" t="s">
         <v>74</v>
       </c>
@@ -3016,117 +3016,117 @@
       <c r="U34" s="6"/>
     </row>
     <row r="35" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="64"/>
+      <c r="A35" s="67"/>
       <c r="B35" s="34" t="s">
         <v>75</v>
       </c>
       <c r="C35" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="86" t="s">
+      <c r="D35" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="E35" s="65"/>
-      <c r="F35" s="65"/>
-      <c r="G35" s="65"/>
-      <c r="H35" s="65"/>
-      <c r="I35" s="65"/>
-      <c r="J35" s="65"/>
-      <c r="K35" s="65"/>
-      <c r="L35" s="65"/>
-      <c r="M35" s="65"/>
-      <c r="N35" s="65"/>
-      <c r="O35" s="65"/>
-      <c r="P35" s="65"/>
-      <c r="Q35" s="65"/>
-      <c r="R35" s="65"/>
-      <c r="S35" s="65"/>
-      <c r="T35" s="65"/>
-      <c r="U35" s="66"/>
+      <c r="E35" s="79"/>
+      <c r="F35" s="79"/>
+      <c r="G35" s="79"/>
+      <c r="H35" s="79"/>
+      <c r="I35" s="79"/>
+      <c r="J35" s="79"/>
+      <c r="K35" s="79"/>
+      <c r="L35" s="79"/>
+      <c r="M35" s="79"/>
+      <c r="N35" s="79"/>
+      <c r="O35" s="79"/>
+      <c r="P35" s="79"/>
+      <c r="Q35" s="79"/>
+      <c r="R35" s="79"/>
+      <c r="S35" s="79"/>
+      <c r="T35" s="79"/>
+      <c r="U35" s="80"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="64"/>
+      <c r="A36" s="67"/>
       <c r="B36" s="34" t="s">
         <v>76</v>
       </c>
       <c r="C36" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="D36" s="87"/>
-      <c r="E36" s="67"/>
-      <c r="F36" s="67"/>
-      <c r="G36" s="67"/>
-      <c r="H36" s="67"/>
-      <c r="I36" s="67"/>
-      <c r="J36" s="67"/>
-      <c r="K36" s="67"/>
-      <c r="L36" s="67"/>
-      <c r="M36" s="67"/>
-      <c r="N36" s="67"/>
-      <c r="O36" s="67"/>
-      <c r="P36" s="67"/>
-      <c r="Q36" s="67"/>
-      <c r="R36" s="67"/>
-      <c r="S36" s="67"/>
-      <c r="T36" s="67"/>
-      <c r="U36" s="68"/>
+      <c r="D36" s="81"/>
+      <c r="E36" s="82"/>
+      <c r="F36" s="82"/>
+      <c r="G36" s="82"/>
+      <c r="H36" s="82"/>
+      <c r="I36" s="82"/>
+      <c r="J36" s="82"/>
+      <c r="K36" s="82"/>
+      <c r="L36" s="82"/>
+      <c r="M36" s="82"/>
+      <c r="N36" s="82"/>
+      <c r="O36" s="82"/>
+      <c r="P36" s="82"/>
+      <c r="Q36" s="82"/>
+      <c r="R36" s="82"/>
+      <c r="S36" s="82"/>
+      <c r="T36" s="82"/>
+      <c r="U36" s="83"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="64"/>
+      <c r="A37" s="67"/>
       <c r="B37" s="34" t="s">
         <v>77</v>
       </c>
       <c r="C37" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="D37" s="87"/>
-      <c r="E37" s="67"/>
-      <c r="F37" s="67"/>
-      <c r="G37" s="67"/>
-      <c r="H37" s="67"/>
-      <c r="I37" s="67"/>
-      <c r="J37" s="67"/>
-      <c r="K37" s="67"/>
-      <c r="L37" s="67"/>
-      <c r="M37" s="67"/>
-      <c r="N37" s="67"/>
-      <c r="O37" s="67"/>
-      <c r="P37" s="67"/>
-      <c r="Q37" s="67"/>
-      <c r="R37" s="67"/>
-      <c r="S37" s="67"/>
-      <c r="T37" s="67"/>
-      <c r="U37" s="68"/>
+      <c r="D37" s="81"/>
+      <c r="E37" s="82"/>
+      <c r="F37" s="82"/>
+      <c r="G37" s="82"/>
+      <c r="H37" s="82"/>
+      <c r="I37" s="82"/>
+      <c r="J37" s="82"/>
+      <c r="K37" s="82"/>
+      <c r="L37" s="82"/>
+      <c r="M37" s="82"/>
+      <c r="N37" s="82"/>
+      <c r="O37" s="82"/>
+      <c r="P37" s="82"/>
+      <c r="Q37" s="82"/>
+      <c r="R37" s="82"/>
+      <c r="S37" s="82"/>
+      <c r="T37" s="82"/>
+      <c r="U37" s="83"/>
     </row>
     <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="64"/>
+      <c r="A38" s="67"/>
       <c r="B38" s="34" t="s">
         <v>78</v>
       </c>
       <c r="C38" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="D38" s="87"/>
-      <c r="E38" s="67"/>
-      <c r="F38" s="67"/>
-      <c r="G38" s="67"/>
-      <c r="H38" s="67"/>
-      <c r="I38" s="67"/>
-      <c r="J38" s="67"/>
-      <c r="K38" s="67"/>
-      <c r="L38" s="67"/>
-      <c r="M38" s="67"/>
-      <c r="N38" s="67"/>
-      <c r="O38" s="67"/>
-      <c r="P38" s="67"/>
-      <c r="Q38" s="67"/>
-      <c r="R38" s="67"/>
-      <c r="S38" s="67"/>
-      <c r="T38" s="67"/>
-      <c r="U38" s="68"/>
+      <c r="D38" s="81"/>
+      <c r="E38" s="82"/>
+      <c r="F38" s="82"/>
+      <c r="G38" s="82"/>
+      <c r="H38" s="82"/>
+      <c r="I38" s="82"/>
+      <c r="J38" s="82"/>
+      <c r="K38" s="82"/>
+      <c r="L38" s="82"/>
+      <c r="M38" s="82"/>
+      <c r="N38" s="82"/>
+      <c r="O38" s="82"/>
+      <c r="P38" s="82"/>
+      <c r="Q38" s="82"/>
+      <c r="R38" s="82"/>
+      <c r="S38" s="82"/>
+      <c r="T38" s="82"/>
+      <c r="U38" s="83"/>
     </row>
     <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="71">
+      <c r="A39" s="63">
         <v>6</v>
       </c>
       <c r="B39" s="34" t="s">
@@ -3135,81 +3135,81 @@
       <c r="C39" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="87"/>
-      <c r="E39" s="67"/>
-      <c r="F39" s="67"/>
-      <c r="G39" s="67"/>
-      <c r="H39" s="67"/>
-      <c r="I39" s="67"/>
-      <c r="J39" s="67"/>
-      <c r="K39" s="67"/>
-      <c r="L39" s="67"/>
-      <c r="M39" s="67"/>
-      <c r="N39" s="67"/>
-      <c r="O39" s="67"/>
-      <c r="P39" s="67"/>
-      <c r="Q39" s="67"/>
-      <c r="R39" s="67"/>
-      <c r="S39" s="67"/>
-      <c r="T39" s="67"/>
-      <c r="U39" s="68"/>
+      <c r="D39" s="81"/>
+      <c r="E39" s="82"/>
+      <c r="F39" s="82"/>
+      <c r="G39" s="82"/>
+      <c r="H39" s="82"/>
+      <c r="I39" s="82"/>
+      <c r="J39" s="82"/>
+      <c r="K39" s="82"/>
+      <c r="L39" s="82"/>
+      <c r="M39" s="82"/>
+      <c r="N39" s="82"/>
+      <c r="O39" s="82"/>
+      <c r="P39" s="82"/>
+      <c r="Q39" s="82"/>
+      <c r="R39" s="82"/>
+      <c r="S39" s="82"/>
+      <c r="T39" s="82"/>
+      <c r="U39" s="83"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="71"/>
+      <c r="A40" s="63"/>
       <c r="B40" s="34" t="s">
         <v>80</v>
       </c>
       <c r="C40" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="D40" s="87"/>
-      <c r="E40" s="67"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="67"/>
-      <c r="H40" s="67"/>
-      <c r="I40" s="67"/>
-      <c r="J40" s="67"/>
-      <c r="K40" s="67"/>
-      <c r="L40" s="67"/>
-      <c r="M40" s="67"/>
-      <c r="N40" s="67"/>
-      <c r="O40" s="67"/>
-      <c r="P40" s="67"/>
-      <c r="Q40" s="67"/>
-      <c r="R40" s="67"/>
-      <c r="S40" s="67"/>
-      <c r="T40" s="67"/>
-      <c r="U40" s="68"/>
+      <c r="D40" s="81"/>
+      <c r="E40" s="82"/>
+      <c r="F40" s="82"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="82"/>
+      <c r="I40" s="82"/>
+      <c r="J40" s="82"/>
+      <c r="K40" s="82"/>
+      <c r="L40" s="82"/>
+      <c r="M40" s="82"/>
+      <c r="N40" s="82"/>
+      <c r="O40" s="82"/>
+      <c r="P40" s="82"/>
+      <c r="Q40" s="82"/>
+      <c r="R40" s="82"/>
+      <c r="S40" s="82"/>
+      <c r="T40" s="82"/>
+      <c r="U40" s="83"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="71"/>
+      <c r="A41" s="63"/>
       <c r="B41" s="34" t="s">
         <v>81</v>
       </c>
       <c r="C41" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="D41" s="88"/>
-      <c r="E41" s="69"/>
-      <c r="F41" s="69"/>
-      <c r="G41" s="69"/>
-      <c r="H41" s="69"/>
-      <c r="I41" s="69"/>
-      <c r="J41" s="69"/>
-      <c r="K41" s="69"/>
-      <c r="L41" s="69"/>
-      <c r="M41" s="69"/>
-      <c r="N41" s="69"/>
-      <c r="O41" s="69"/>
-      <c r="P41" s="69"/>
-      <c r="Q41" s="69"/>
-      <c r="R41" s="69"/>
-      <c r="S41" s="69"/>
-      <c r="T41" s="69"/>
-      <c r="U41" s="70"/>
+      <c r="D41" s="84"/>
+      <c r="E41" s="85"/>
+      <c r="F41" s="85"/>
+      <c r="G41" s="85"/>
+      <c r="H41" s="85"/>
+      <c r="I41" s="85"/>
+      <c r="J41" s="85"/>
+      <c r="K41" s="85"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="85"/>
+      <c r="N41" s="85"/>
+      <c r="O41" s="85"/>
+      <c r="P41" s="85"/>
+      <c r="Q41" s="85"/>
+      <c r="R41" s="85"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="85"/>
+      <c r="U41" s="86"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="71"/>
+      <c r="A42" s="63"/>
       <c r="B42" s="35" t="s">
         <v>82</v>
       </c>
@@ -3268,7 +3268,7 @@
       </c>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="71"/>
+      <c r="A43" s="63"/>
       <c r="B43" s="35" t="s">
         <v>83</v>
       </c>
@@ -3315,7 +3315,7 @@
       <c r="U43" s="15"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="71"/>
+      <c r="A44" s="63"/>
       <c r="B44" s="37" t="s">
         <v>84</v>
       </c>
@@ -3360,7 +3360,7 @@
       <c r="U44" s="26"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="71"/>
+      <c r="A45" s="63"/>
       <c r="B45" s="35" t="s">
         <v>86</v>
       </c>
@@ -3387,7 +3387,7 @@
       <c r="U45" s="15"/>
     </row>
     <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="64">
+      <c r="A46" s="67">
         <v>7</v>
       </c>
       <c r="B46" s="39" t="s">
@@ -3436,7 +3436,7 @@
       <c r="U46" s="6"/>
     </row>
     <row r="47" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="64"/>
+      <c r="A47" s="67"/>
       <c r="B47" s="39" t="s">
         <v>88</v>
       </c>
@@ -3465,7 +3465,7 @@
       <c r="U47" s="6"/>
     </row>
     <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="64"/>
+      <c r="A48" s="67"/>
       <c r="B48" s="39" t="s">
         <v>89</v>
       </c>
@@ -3512,7 +3512,7 @@
       <c r="U48" s="6"/>
     </row>
     <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="64"/>
+      <c r="A49" s="67"/>
       <c r="B49" s="39" t="s">
         <v>90</v>
       </c>
@@ -3541,7 +3541,7 @@
       <c r="U49" s="6"/>
     </row>
     <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="64"/>
+      <c r="A50" s="67"/>
       <c r="B50" s="39" t="s">
         <v>91</v>
       </c>
@@ -3588,7 +3588,7 @@
       <c r="U50" s="6"/>
     </row>
     <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="64"/>
+      <c r="A51" s="67"/>
       <c r="B51" s="39" t="s">
         <v>92</v>
       </c>
@@ -3615,7 +3615,7 @@
       <c r="U51" s="6"/>
     </row>
     <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="64"/>
+      <c r="A52" s="67"/>
       <c r="B52" s="39" t="s">
         <v>93</v>
       </c>
@@ -3642,7 +3642,7 @@
       <c r="U52" s="6"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="71">
+      <c r="A53" s="63">
         <v>8</v>
       </c>
       <c r="B53" s="35" t="s">
@@ -3691,7 +3691,7 @@
       <c r="U53" s="15"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="71"/>
+      <c r="A54" s="63"/>
       <c r="B54" s="35" t="s">
         <v>95</v>
       </c>
@@ -3738,7 +3738,7 @@
       <c r="U54" s="15"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="71"/>
+      <c r="A55" s="63"/>
       <c r="B55" s="35" t="s">
         <v>96</v>
       </c>
@@ -3785,7 +3785,7 @@
       <c r="U55" s="15"/>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="71"/>
+      <c r="A56" s="63"/>
       <c r="B56" s="35" t="s">
         <v>97</v>
       </c>
@@ -3844,7 +3844,7 @@
       </c>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="71"/>
+      <c r="A57" s="63"/>
       <c r="B57" s="35" t="s">
         <v>98</v>
       </c>
@@ -3891,7 +3891,7 @@
       <c r="U57" s="15"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="71"/>
+      <c r="A58" s="63"/>
       <c r="B58" s="35" t="s">
         <v>99</v>
       </c>
@@ -3901,33 +3901,15 @@
       <c r="D58" s="11"/>
       <c r="E58" s="13"/>
       <c r="F58" s="14"/>
-      <c r="G58" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="H58" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="I58" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="J58" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K58" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="L58" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="M58" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="N58" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="O58" s="15" t="s">
-        <v>85</v>
-      </c>
+      <c r="G58" s="11"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="15"/>
+      <c r="J58" s="11"/>
+      <c r="K58" s="13"/>
+      <c r="L58" s="15"/>
+      <c r="M58" s="11"/>
+      <c r="N58" s="13"/>
+      <c r="O58" s="15"/>
       <c r="P58" s="11"/>
       <c r="Q58" s="13"/>
       <c r="R58" s="15"/>
@@ -3936,7 +3918,7 @@
       <c r="U58" s="15"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="71"/>
+      <c r="A59" s="63"/>
       <c r="B59" s="35" t="s">
         <v>100</v>
       </c>
@@ -3963,7 +3945,7 @@
       <c r="U59" s="15"/>
     </row>
     <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="64">
+      <c r="A60" s="67">
         <v>9</v>
       </c>
       <c r="B60" s="39" t="s">
@@ -4012,7 +3994,7 @@
       <c r="U60" s="6"/>
     </row>
     <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="64"/>
+      <c r="A61" s="67"/>
       <c r="B61" s="39" t="s">
         <v>102</v>
       </c>
@@ -4059,7 +4041,7 @@
       <c r="U61" s="6"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="64"/>
+      <c r="A62" s="67"/>
       <c r="B62" s="39" t="s">
         <v>103</v>
       </c>
@@ -4106,7 +4088,7 @@
       <c r="U62" s="6"/>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="64"/>
+      <c r="A63" s="67"/>
       <c r="B63" s="39" t="s">
         <v>104</v>
       </c>
@@ -4165,7 +4147,7 @@
       </c>
     </row>
     <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="64"/>
+      <c r="A64" s="67"/>
       <c r="B64" s="39" t="s">
         <v>105</v>
       </c>
@@ -4212,7 +4194,7 @@
       <c r="U64" s="5"/>
     </row>
     <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="64"/>
+      <c r="A65" s="67"/>
       <c r="B65" s="39" t="s">
         <v>106</v>
       </c>
@@ -4239,7 +4221,7 @@
       <c r="U65" s="5"/>
     </row>
     <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="64"/>
+      <c r="A66" s="67"/>
       <c r="B66" s="39" t="s">
         <v>107</v>
       </c>
@@ -4266,7 +4248,7 @@
       <c r="U66" s="5"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="71">
+      <c r="A67" s="63">
         <v>10</v>
       </c>
       <c r="B67" s="35" t="s">
@@ -4315,7 +4297,7 @@
       <c r="U67" s="14"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="71"/>
+      <c r="A68" s="63"/>
       <c r="B68" s="35" t="s">
         <v>109</v>
       </c>
@@ -4344,7 +4326,7 @@
       <c r="U68" s="14"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="71"/>
+      <c r="A69" s="63"/>
       <c r="B69" s="35" t="s">
         <v>110</v>
       </c>
@@ -4391,7 +4373,7 @@
       <c r="U69" s="14"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="71"/>
+      <c r="A70" s="63"/>
       <c r="B70" s="35" t="s">
         <v>111</v>
       </c>
@@ -4432,7 +4414,7 @@
       </c>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="71"/>
+      <c r="A71" s="63"/>
       <c r="B71" s="35" t="s">
         <v>112</v>
       </c>
@@ -4479,7 +4461,7 @@
       <c r="U71" s="14"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="71"/>
+      <c r="A72" s="63"/>
       <c r="B72" s="35" t="s">
         <v>113</v>
       </c>
@@ -4489,15 +4471,33 @@
       <c r="D72" s="11"/>
       <c r="E72" s="13"/>
       <c r="F72" s="14"/>
-      <c r="G72" s="11"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="15"/>
-      <c r="J72" s="11"/>
-      <c r="K72" s="13"/>
-      <c r="L72" s="15"/>
-      <c r="M72" s="11"/>
-      <c r="N72" s="13"/>
-      <c r="O72" s="15"/>
+      <c r="G72" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H72" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="I72" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="J72" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="K72" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="L72" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="M72" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N72" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="O72" s="15" t="s">
+        <v>85</v>
+      </c>
       <c r="P72" s="11"/>
       <c r="Q72" s="13"/>
       <c r="R72" s="14"/>
@@ -4506,7 +4506,7 @@
       <c r="U72" s="14"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="71"/>
+      <c r="A73" s="63"/>
       <c r="B73" s="35" t="s">
         <v>114</v>
       </c>
@@ -4533,7 +4533,7 @@
       <c r="U73" s="14"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="64">
+      <c r="A74" s="67">
         <v>11</v>
       </c>
       <c r="B74" s="39" t="s">
@@ -4582,7 +4582,7 @@
       <c r="U74" s="5"/>
     </row>
     <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A75" s="64"/>
+      <c r="A75" s="67"/>
       <c r="B75" s="39" t="s">
         <v>116</v>
       </c>
@@ -4611,7 +4611,7 @@
       <c r="U75" s="5"/>
     </row>
     <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A76" s="64"/>
+      <c r="A76" s="67"/>
       <c r="B76" s="39" t="s">
         <v>117</v>
       </c>
@@ -4658,7 +4658,7 @@
       <c r="U76" s="5"/>
     </row>
     <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A77" s="64"/>
+      <c r="A77" s="67"/>
       <c r="B77" s="39" t="s">
         <v>118</v>
       </c>
@@ -4687,7 +4687,7 @@
       <c r="U77" s="6"/>
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A78" s="64"/>
+      <c r="A78" s="67"/>
       <c r="B78" s="39" t="s">
         <v>119</v>
       </c>
@@ -4734,7 +4734,7 @@
       <c r="U78" s="6"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A79" s="64"/>
+      <c r="A79" s="67"/>
       <c r="B79" s="39" t="s">
         <v>120</v>
       </c>
@@ -4761,7 +4761,7 @@
       <c r="U79" s="6"/>
     </row>
     <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A80" s="64"/>
+      <c r="A80" s="67"/>
       <c r="B80" s="39" t="s">
         <v>121</v>
       </c>
@@ -4788,7 +4788,7 @@
       <c r="U80" s="6"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="71">
+      <c r="A81" s="63">
         <v>12</v>
       </c>
       <c r="B81" s="35" t="s">
@@ -4797,191 +4797,191 @@
       <c r="C81" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="D81" s="89" t="s">
+      <c r="D81" s="68" t="s">
         <v>123</v>
       </c>
-      <c r="E81" s="80"/>
-      <c r="F81" s="80"/>
-      <c r="G81" s="80"/>
-      <c r="H81" s="80"/>
-      <c r="I81" s="80"/>
-      <c r="J81" s="80"/>
-      <c r="K81" s="80"/>
-      <c r="L81" s="80"/>
-      <c r="M81" s="80"/>
-      <c r="N81" s="80"/>
-      <c r="O81" s="80"/>
-      <c r="P81" s="80"/>
-      <c r="Q81" s="80"/>
-      <c r="R81" s="80"/>
-      <c r="S81" s="80"/>
-      <c r="T81" s="80"/>
-      <c r="U81" s="81"/>
+      <c r="E81" s="69"/>
+      <c r="F81" s="69"/>
+      <c r="G81" s="69"/>
+      <c r="H81" s="69"/>
+      <c r="I81" s="69"/>
+      <c r="J81" s="69"/>
+      <c r="K81" s="69"/>
+      <c r="L81" s="69"/>
+      <c r="M81" s="69"/>
+      <c r="N81" s="69"/>
+      <c r="O81" s="69"/>
+      <c r="P81" s="69"/>
+      <c r="Q81" s="69"/>
+      <c r="R81" s="69"/>
+      <c r="S81" s="69"/>
+      <c r="T81" s="69"/>
+      <c r="U81" s="70"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="71"/>
+      <c r="A82" s="63"/>
       <c r="B82" s="35" t="s">
         <v>124</v>
       </c>
       <c r="C82" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="D82" s="90"/>
-      <c r="E82" s="82"/>
-      <c r="F82" s="82"/>
-      <c r="G82" s="82"/>
-      <c r="H82" s="82"/>
-      <c r="I82" s="82"/>
-      <c r="J82" s="82"/>
-      <c r="K82" s="82"/>
-      <c r="L82" s="82"/>
-      <c r="M82" s="82"/>
-      <c r="N82" s="82"/>
-      <c r="O82" s="82"/>
-      <c r="P82" s="82"/>
-      <c r="Q82" s="82"/>
-      <c r="R82" s="82"/>
-      <c r="S82" s="82"/>
-      <c r="T82" s="82"/>
-      <c r="U82" s="83"/>
+      <c r="D82" s="71"/>
+      <c r="E82" s="72"/>
+      <c r="F82" s="72"/>
+      <c r="G82" s="72"/>
+      <c r="H82" s="72"/>
+      <c r="I82" s="72"/>
+      <c r="J82" s="72"/>
+      <c r="K82" s="72"/>
+      <c r="L82" s="72"/>
+      <c r="M82" s="72"/>
+      <c r="N82" s="72"/>
+      <c r="O82" s="72"/>
+      <c r="P82" s="72"/>
+      <c r="Q82" s="72"/>
+      <c r="R82" s="72"/>
+      <c r="S82" s="72"/>
+      <c r="T82" s="72"/>
+      <c r="U82" s="73"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="71"/>
+      <c r="A83" s="63"/>
       <c r="B83" s="35" t="s">
         <v>125</v>
       </c>
       <c r="C83" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="D83" s="90"/>
-      <c r="E83" s="82"/>
-      <c r="F83" s="82"/>
-      <c r="G83" s="82"/>
-      <c r="H83" s="82"/>
-      <c r="I83" s="82"/>
-      <c r="J83" s="82"/>
-      <c r="K83" s="82"/>
-      <c r="L83" s="82"/>
-      <c r="M83" s="82"/>
-      <c r="N83" s="82"/>
-      <c r="O83" s="82"/>
-      <c r="P83" s="82"/>
-      <c r="Q83" s="82"/>
-      <c r="R83" s="82"/>
-      <c r="S83" s="82"/>
-      <c r="T83" s="82"/>
-      <c r="U83" s="83"/>
+      <c r="D83" s="71"/>
+      <c r="E83" s="72"/>
+      <c r="F83" s="72"/>
+      <c r="G83" s="72"/>
+      <c r="H83" s="72"/>
+      <c r="I83" s="72"/>
+      <c r="J83" s="72"/>
+      <c r="K83" s="72"/>
+      <c r="L83" s="72"/>
+      <c r="M83" s="72"/>
+      <c r="N83" s="72"/>
+      <c r="O83" s="72"/>
+      <c r="P83" s="72"/>
+      <c r="Q83" s="72"/>
+      <c r="R83" s="72"/>
+      <c r="S83" s="72"/>
+      <c r="T83" s="72"/>
+      <c r="U83" s="73"/>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="71"/>
+      <c r="A84" s="63"/>
       <c r="B84" s="35" t="s">
         <v>126</v>
       </c>
       <c r="C84" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="D84" s="90"/>
-      <c r="E84" s="82"/>
-      <c r="F84" s="82"/>
-      <c r="G84" s="82"/>
-      <c r="H84" s="82"/>
-      <c r="I84" s="82"/>
-      <c r="J84" s="82"/>
-      <c r="K84" s="82"/>
-      <c r="L84" s="82"/>
-      <c r="M84" s="82"/>
-      <c r="N84" s="82"/>
-      <c r="O84" s="82"/>
-      <c r="P84" s="82"/>
-      <c r="Q84" s="82"/>
-      <c r="R84" s="82"/>
-      <c r="S84" s="82"/>
-      <c r="T84" s="82"/>
-      <c r="U84" s="83"/>
+      <c r="D84" s="71"/>
+      <c r="E84" s="72"/>
+      <c r="F84" s="72"/>
+      <c r="G84" s="72"/>
+      <c r="H84" s="72"/>
+      <c r="I84" s="72"/>
+      <c r="J84" s="72"/>
+      <c r="K84" s="72"/>
+      <c r="L84" s="72"/>
+      <c r="M84" s="72"/>
+      <c r="N84" s="72"/>
+      <c r="O84" s="72"/>
+      <c r="P84" s="72"/>
+      <c r="Q84" s="72"/>
+      <c r="R84" s="72"/>
+      <c r="S84" s="72"/>
+      <c r="T84" s="72"/>
+      <c r="U84" s="73"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="71"/>
+      <c r="A85" s="63"/>
       <c r="B85" s="35" t="s">
         <v>127</v>
       </c>
       <c r="C85" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="D85" s="90"/>
-      <c r="E85" s="82"/>
-      <c r="F85" s="82"/>
-      <c r="G85" s="82"/>
-      <c r="H85" s="82"/>
-      <c r="I85" s="82"/>
-      <c r="J85" s="82"/>
-      <c r="K85" s="82"/>
-      <c r="L85" s="82"/>
-      <c r="M85" s="82"/>
-      <c r="N85" s="82"/>
-      <c r="O85" s="82"/>
-      <c r="P85" s="82"/>
-      <c r="Q85" s="82"/>
-      <c r="R85" s="82"/>
-      <c r="S85" s="82"/>
-      <c r="T85" s="82"/>
-      <c r="U85" s="83"/>
+      <c r="D85" s="71"/>
+      <c r="E85" s="72"/>
+      <c r="F85" s="72"/>
+      <c r="G85" s="72"/>
+      <c r="H85" s="72"/>
+      <c r="I85" s="72"/>
+      <c r="J85" s="72"/>
+      <c r="K85" s="72"/>
+      <c r="L85" s="72"/>
+      <c r="M85" s="72"/>
+      <c r="N85" s="72"/>
+      <c r="O85" s="72"/>
+      <c r="P85" s="72"/>
+      <c r="Q85" s="72"/>
+      <c r="R85" s="72"/>
+      <c r="S85" s="72"/>
+      <c r="T85" s="72"/>
+      <c r="U85" s="73"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="71"/>
+      <c r="A86" s="63"/>
       <c r="B86" s="35" t="s">
         <v>128</v>
       </c>
       <c r="C86" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="D86" s="90"/>
-      <c r="E86" s="82"/>
-      <c r="F86" s="82"/>
-      <c r="G86" s="82"/>
-      <c r="H86" s="82"/>
-      <c r="I86" s="82"/>
-      <c r="J86" s="82"/>
-      <c r="K86" s="82"/>
-      <c r="L86" s="82"/>
-      <c r="M86" s="82"/>
-      <c r="N86" s="82"/>
-      <c r="O86" s="82"/>
-      <c r="P86" s="82"/>
-      <c r="Q86" s="82"/>
-      <c r="R86" s="82"/>
-      <c r="S86" s="82"/>
-      <c r="T86" s="82"/>
-      <c r="U86" s="83"/>
+      <c r="D86" s="71"/>
+      <c r="E86" s="72"/>
+      <c r="F86" s="72"/>
+      <c r="G86" s="72"/>
+      <c r="H86" s="72"/>
+      <c r="I86" s="72"/>
+      <c r="J86" s="72"/>
+      <c r="K86" s="72"/>
+      <c r="L86" s="72"/>
+      <c r="M86" s="72"/>
+      <c r="N86" s="72"/>
+      <c r="O86" s="72"/>
+      <c r="P86" s="72"/>
+      <c r="Q86" s="72"/>
+      <c r="R86" s="72"/>
+      <c r="S86" s="72"/>
+      <c r="T86" s="72"/>
+      <c r="U86" s="73"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="71"/>
+      <c r="A87" s="63"/>
       <c r="B87" s="35" t="s">
         <v>129</v>
       </c>
       <c r="C87" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="D87" s="90"/>
-      <c r="E87" s="82"/>
-      <c r="F87" s="82"/>
-      <c r="G87" s="82"/>
-      <c r="H87" s="82"/>
-      <c r="I87" s="82"/>
-      <c r="J87" s="82"/>
-      <c r="K87" s="82"/>
-      <c r="L87" s="82"/>
-      <c r="M87" s="82"/>
-      <c r="N87" s="82"/>
-      <c r="O87" s="82"/>
-      <c r="P87" s="82"/>
-      <c r="Q87" s="82"/>
-      <c r="R87" s="82"/>
-      <c r="S87" s="82"/>
-      <c r="T87" s="82"/>
-      <c r="U87" s="83"/>
+      <c r="D87" s="71"/>
+      <c r="E87" s="72"/>
+      <c r="F87" s="72"/>
+      <c r="G87" s="72"/>
+      <c r="H87" s="72"/>
+      <c r="I87" s="72"/>
+      <c r="J87" s="72"/>
+      <c r="K87" s="72"/>
+      <c r="L87" s="72"/>
+      <c r="M87" s="72"/>
+      <c r="N87" s="72"/>
+      <c r="O87" s="72"/>
+      <c r="P87" s="72"/>
+      <c r="Q87" s="72"/>
+      <c r="R87" s="72"/>
+      <c r="S87" s="72"/>
+      <c r="T87" s="72"/>
+      <c r="U87" s="73"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A88" s="64">
+      <c r="A88" s="67">
         <v>13</v>
       </c>
       <c r="B88" s="39" t="s">
@@ -4990,189 +4990,189 @@
       <c r="C88" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D88" s="90"/>
-      <c r="E88" s="82"/>
-      <c r="F88" s="82"/>
-      <c r="G88" s="82"/>
-      <c r="H88" s="82"/>
-      <c r="I88" s="82"/>
-      <c r="J88" s="82"/>
-      <c r="K88" s="82"/>
-      <c r="L88" s="82"/>
-      <c r="M88" s="82"/>
-      <c r="N88" s="82"/>
-      <c r="O88" s="82"/>
-      <c r="P88" s="82"/>
-      <c r="Q88" s="82"/>
-      <c r="R88" s="82"/>
-      <c r="S88" s="82"/>
-      <c r="T88" s="82"/>
-      <c r="U88" s="83"/>
+      <c r="D88" s="71"/>
+      <c r="E88" s="72"/>
+      <c r="F88" s="72"/>
+      <c r="G88" s="72"/>
+      <c r="H88" s="72"/>
+      <c r="I88" s="72"/>
+      <c r="J88" s="72"/>
+      <c r="K88" s="72"/>
+      <c r="L88" s="72"/>
+      <c r="M88" s="72"/>
+      <c r="N88" s="72"/>
+      <c r="O88" s="72"/>
+      <c r="P88" s="72"/>
+      <c r="Q88" s="72"/>
+      <c r="R88" s="72"/>
+      <c r="S88" s="72"/>
+      <c r="T88" s="72"/>
+      <c r="U88" s="73"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A89" s="64"/>
+      <c r="A89" s="67"/>
       <c r="B89" s="39" t="s">
         <v>131</v>
       </c>
       <c r="C89" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D89" s="90"/>
-      <c r="E89" s="82"/>
-      <c r="F89" s="82"/>
-      <c r="G89" s="82"/>
-      <c r="H89" s="82"/>
-      <c r="I89" s="82"/>
-      <c r="J89" s="82"/>
-      <c r="K89" s="82"/>
-      <c r="L89" s="82"/>
-      <c r="M89" s="82"/>
-      <c r="N89" s="82"/>
-      <c r="O89" s="82"/>
-      <c r="P89" s="82"/>
-      <c r="Q89" s="82"/>
-      <c r="R89" s="82"/>
-      <c r="S89" s="82"/>
-      <c r="T89" s="82"/>
-      <c r="U89" s="83"/>
+      <c r="D89" s="71"/>
+      <c r="E89" s="72"/>
+      <c r="F89" s="72"/>
+      <c r="G89" s="72"/>
+      <c r="H89" s="72"/>
+      <c r="I89" s="72"/>
+      <c r="J89" s="72"/>
+      <c r="K89" s="72"/>
+      <c r="L89" s="72"/>
+      <c r="M89" s="72"/>
+      <c r="N89" s="72"/>
+      <c r="O89" s="72"/>
+      <c r="P89" s="72"/>
+      <c r="Q89" s="72"/>
+      <c r="R89" s="72"/>
+      <c r="S89" s="72"/>
+      <c r="T89" s="72"/>
+      <c r="U89" s="73"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="64"/>
+      <c r="A90" s="67"/>
       <c r="B90" s="39" t="s">
         <v>132</v>
       </c>
       <c r="C90" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D90" s="90"/>
-      <c r="E90" s="82"/>
-      <c r="F90" s="82"/>
-      <c r="G90" s="82"/>
-      <c r="H90" s="82"/>
-      <c r="I90" s="82"/>
-      <c r="J90" s="82"/>
-      <c r="K90" s="82"/>
-      <c r="L90" s="82"/>
-      <c r="M90" s="82"/>
-      <c r="N90" s="82"/>
-      <c r="O90" s="82"/>
-      <c r="P90" s="82"/>
-      <c r="Q90" s="82"/>
-      <c r="R90" s="82"/>
-      <c r="S90" s="82"/>
-      <c r="T90" s="82"/>
-      <c r="U90" s="83"/>
+      <c r="D90" s="71"/>
+      <c r="E90" s="72"/>
+      <c r="F90" s="72"/>
+      <c r="G90" s="72"/>
+      <c r="H90" s="72"/>
+      <c r="I90" s="72"/>
+      <c r="J90" s="72"/>
+      <c r="K90" s="72"/>
+      <c r="L90" s="72"/>
+      <c r="M90" s="72"/>
+      <c r="N90" s="72"/>
+      <c r="O90" s="72"/>
+      <c r="P90" s="72"/>
+      <c r="Q90" s="72"/>
+      <c r="R90" s="72"/>
+      <c r="S90" s="72"/>
+      <c r="T90" s="72"/>
+      <c r="U90" s="73"/>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="64"/>
+      <c r="A91" s="67"/>
       <c r="B91" s="39" t="s">
         <v>133</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D91" s="90"/>
-      <c r="E91" s="82"/>
-      <c r="F91" s="82"/>
-      <c r="G91" s="82"/>
-      <c r="H91" s="82"/>
-      <c r="I91" s="82"/>
-      <c r="J91" s="82"/>
-      <c r="K91" s="82"/>
-      <c r="L91" s="82"/>
-      <c r="M91" s="82"/>
-      <c r="N91" s="82"/>
-      <c r="O91" s="82"/>
-      <c r="P91" s="82"/>
-      <c r="Q91" s="82"/>
-      <c r="R91" s="82"/>
-      <c r="S91" s="82"/>
-      <c r="T91" s="82"/>
-      <c r="U91" s="83"/>
+      <c r="D91" s="71"/>
+      <c r="E91" s="72"/>
+      <c r="F91" s="72"/>
+      <c r="G91" s="72"/>
+      <c r="H91" s="72"/>
+      <c r="I91" s="72"/>
+      <c r="J91" s="72"/>
+      <c r="K91" s="72"/>
+      <c r="L91" s="72"/>
+      <c r="M91" s="72"/>
+      <c r="N91" s="72"/>
+      <c r="O91" s="72"/>
+      <c r="P91" s="72"/>
+      <c r="Q91" s="72"/>
+      <c r="R91" s="72"/>
+      <c r="S91" s="72"/>
+      <c r="T91" s="72"/>
+      <c r="U91" s="73"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A92" s="64"/>
+      <c r="A92" s="67"/>
       <c r="B92" s="39" t="s">
         <v>134</v>
       </c>
       <c r="C92" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D92" s="90"/>
-      <c r="E92" s="82"/>
-      <c r="F92" s="82"/>
-      <c r="G92" s="82"/>
-      <c r="H92" s="82"/>
-      <c r="I92" s="82"/>
-      <c r="J92" s="82"/>
-      <c r="K92" s="82"/>
-      <c r="L92" s="82"/>
-      <c r="M92" s="82"/>
-      <c r="N92" s="82"/>
-      <c r="O92" s="82"/>
-      <c r="P92" s="82"/>
-      <c r="Q92" s="82"/>
-      <c r="R92" s="82"/>
-      <c r="S92" s="82"/>
-      <c r="T92" s="82"/>
-      <c r="U92" s="83"/>
+      <c r="D92" s="71"/>
+      <c r="E92" s="72"/>
+      <c r="F92" s="72"/>
+      <c r="G92" s="72"/>
+      <c r="H92" s="72"/>
+      <c r="I92" s="72"/>
+      <c r="J92" s="72"/>
+      <c r="K92" s="72"/>
+      <c r="L92" s="72"/>
+      <c r="M92" s="72"/>
+      <c r="N92" s="72"/>
+      <c r="O92" s="72"/>
+      <c r="P92" s="72"/>
+      <c r="Q92" s="72"/>
+      <c r="R92" s="72"/>
+      <c r="S92" s="72"/>
+      <c r="T92" s="72"/>
+      <c r="U92" s="73"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A93" s="64"/>
+      <c r="A93" s="67"/>
       <c r="B93" s="39" t="s">
         <v>135</v>
       </c>
       <c r="C93" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D93" s="90"/>
-      <c r="E93" s="82"/>
-      <c r="F93" s="82"/>
-      <c r="G93" s="82"/>
-      <c r="H93" s="82"/>
-      <c r="I93" s="82"/>
-      <c r="J93" s="82"/>
-      <c r="K93" s="82"/>
-      <c r="L93" s="82"/>
-      <c r="M93" s="82"/>
-      <c r="N93" s="82"/>
-      <c r="O93" s="82"/>
-      <c r="P93" s="82"/>
-      <c r="Q93" s="82"/>
-      <c r="R93" s="82"/>
-      <c r="S93" s="82"/>
-      <c r="T93" s="82"/>
-      <c r="U93" s="83"/>
+      <c r="D93" s="71"/>
+      <c r="E93" s="72"/>
+      <c r="F93" s="72"/>
+      <c r="G93" s="72"/>
+      <c r="H93" s="72"/>
+      <c r="I93" s="72"/>
+      <c r="J93" s="72"/>
+      <c r="K93" s="72"/>
+      <c r="L93" s="72"/>
+      <c r="M93" s="72"/>
+      <c r="N93" s="72"/>
+      <c r="O93" s="72"/>
+      <c r="P93" s="72"/>
+      <c r="Q93" s="72"/>
+      <c r="R93" s="72"/>
+      <c r="S93" s="72"/>
+      <c r="T93" s="72"/>
+      <c r="U93" s="73"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A94" s="64"/>
+      <c r="A94" s="67"/>
       <c r="B94" s="39" t="s">
         <v>136</v>
       </c>
       <c r="C94" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D94" s="91"/>
-      <c r="E94" s="84"/>
-      <c r="F94" s="84"/>
-      <c r="G94" s="84"/>
-      <c r="H94" s="84"/>
-      <c r="I94" s="84"/>
-      <c r="J94" s="84"/>
-      <c r="K94" s="84"/>
-      <c r="L94" s="84"/>
-      <c r="M94" s="84"/>
-      <c r="N94" s="84"/>
-      <c r="O94" s="84"/>
-      <c r="P94" s="84"/>
-      <c r="Q94" s="84"/>
-      <c r="R94" s="84"/>
-      <c r="S94" s="84"/>
-      <c r="T94" s="84"/>
-      <c r="U94" s="85"/>
+      <c r="D94" s="74"/>
+      <c r="E94" s="75"/>
+      <c r="F94" s="75"/>
+      <c r="G94" s="75"/>
+      <c r="H94" s="75"/>
+      <c r="I94" s="75"/>
+      <c r="J94" s="75"/>
+      <c r="K94" s="75"/>
+      <c r="L94" s="75"/>
+      <c r="M94" s="75"/>
+      <c r="N94" s="75"/>
+      <c r="O94" s="75"/>
+      <c r="P94" s="75"/>
+      <c r="Q94" s="75"/>
+      <c r="R94" s="75"/>
+      <c r="S94" s="75"/>
+      <c r="T94" s="75"/>
+      <c r="U94" s="76"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="71">
+      <c r="A95" s="63">
         <v>14</v>
       </c>
       <c r="B95" s="35" t="s">
@@ -5205,7 +5205,7 @@
       <c r="U95" s="15"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="71"/>
+      <c r="A96" s="63"/>
       <c r="B96" s="35" t="s">
         <v>139</v>
       </c>
@@ -5236,7 +5236,7 @@
       <c r="U96" s="15"/>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="71"/>
+      <c r="A97" s="63"/>
       <c r="B97" s="35" t="s">
         <v>140</v>
       </c>
@@ -5267,7 +5267,7 @@
       <c r="U97" s="15"/>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="71"/>
+      <c r="A98" s="63"/>
       <c r="B98" s="35" t="s">
         <v>141</v>
       </c>
@@ -5298,7 +5298,7 @@
       <c r="U98" s="15"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="71"/>
+      <c r="A99" s="63"/>
       <c r="B99" s="35" t="s">
         <v>142</v>
       </c>
@@ -5329,7 +5329,7 @@
       <c r="U99" s="15"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="71"/>
+      <c r="A100" s="63"/>
       <c r="B100" s="35" t="s">
         <v>143</v>
       </c>
@@ -5360,7 +5360,7 @@
       <c r="U100" s="15"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="71"/>
+      <c r="A101" s="63"/>
       <c r="B101" s="35" t="s">
         <v>144</v>
       </c>
@@ -5391,7 +5391,7 @@
       <c r="U101" s="15"/>
     </row>
     <row r="102" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="64">
+      <c r="A102" s="67">
         <v>15</v>
       </c>
       <c r="B102" s="39" t="s">
@@ -5424,7 +5424,7 @@
       <c r="U102" s="6"/>
     </row>
     <row r="103" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="64"/>
+      <c r="A103" s="67"/>
       <c r="B103" s="39" t="s">
         <v>146</v>
       </c>
@@ -5455,7 +5455,7 @@
       <c r="U103" s="6"/>
     </row>
     <row r="104" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="64"/>
+      <c r="A104" s="67"/>
       <c r="B104" s="39" t="s">
         <v>147</v>
       </c>
@@ -5486,7 +5486,7 @@
       <c r="U104" s="6"/>
     </row>
     <row r="105" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="64"/>
+      <c r="A105" s="67"/>
       <c r="B105" s="39" t="s">
         <v>148</v>
       </c>
@@ -5517,7 +5517,7 @@
       <c r="U105" s="6"/>
     </row>
     <row r="106" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="64"/>
+      <c r="A106" s="67"/>
       <c r="B106" s="39" t="s">
         <v>149</v>
       </c>
@@ -5548,7 +5548,7 @@
       <c r="U106" s="6"/>
     </row>
     <row r="107" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="64"/>
+      <c r="A107" s="67"/>
       <c r="B107" s="39" t="s">
         <v>150</v>
       </c>
@@ -5579,7 +5579,7 @@
       <c r="U107" s="6"/>
     </row>
     <row r="108" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="64"/>
+      <c r="A108" s="67"/>
       <c r="B108" s="39" t="s">
         <v>151</v>
       </c>
@@ -5610,7 +5610,7 @@
       <c r="U108" s="6"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="71">
+      <c r="A109" s="63">
         <v>16</v>
       </c>
       <c r="B109" s="35" t="s">
@@ -5643,7 +5643,7 @@
       <c r="U109" s="14"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="71"/>
+      <c r="A110" s="63"/>
       <c r="B110" s="35" t="s">
         <v>153</v>
       </c>
@@ -5674,7 +5674,7 @@
       <c r="U110" s="14"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="71"/>
+      <c r="A111" s="63"/>
       <c r="B111" s="35" t="s">
         <v>154</v>
       </c>
@@ -5705,7 +5705,7 @@
       <c r="U111" s="14"/>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="71"/>
+      <c r="A112" s="63"/>
       <c r="B112" s="35" t="s">
         <v>155</v>
       </c>
@@ -5736,7 +5736,7 @@
       <c r="U112" s="14"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="71"/>
+      <c r="A113" s="63"/>
       <c r="B113" s="35" t="s">
         <v>156</v>
       </c>
@@ -5767,7 +5767,7 @@
       <c r="U113" s="14"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="71"/>
+      <c r="A114" s="63"/>
       <c r="B114" s="35" t="s">
         <v>157</v>
       </c>
@@ -5798,7 +5798,7 @@
       <c r="U114" s="14"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="71"/>
+      <c r="A115" s="63"/>
       <c r="B115" s="35" t="s">
         <v>158</v>
       </c>
@@ -5829,7 +5829,7 @@
       <c r="U115" s="14"/>
     </row>
     <row r="116" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A116" s="64">
+      <c r="A116" s="67">
         <v>17</v>
       </c>
       <c r="B116" s="39" t="s">
@@ -5862,7 +5862,7 @@
       <c r="U116" s="6"/>
     </row>
     <row r="117" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A117" s="64"/>
+      <c r="A117" s="67"/>
       <c r="B117" s="39" t="s">
         <v>160</v>
       </c>
@@ -5893,7 +5893,7 @@
       <c r="U117" s="6"/>
     </row>
     <row r="118" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="64"/>
+      <c r="A118" s="67"/>
       <c r="B118" s="39" t="s">
         <v>161</v>
       </c>
@@ -5924,7 +5924,7 @@
       <c r="U118" s="6"/>
     </row>
     <row r="119" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="64"/>
+      <c r="A119" s="67"/>
       <c r="B119" s="39" t="s">
         <v>162</v>
       </c>
@@ -5955,7 +5955,7 @@
       <c r="U119" s="6"/>
     </row>
     <row r="120" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="64"/>
+      <c r="A120" s="67"/>
       <c r="B120" s="39" t="s">
         <v>163</v>
       </c>
@@ -5986,7 +5986,7 @@
       <c r="U120" s="6"/>
     </row>
     <row r="121" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="64"/>
+      <c r="A121" s="67"/>
       <c r="B121" s="39" t="s">
         <v>164</v>
       </c>
@@ -6017,7 +6017,7 @@
       <c r="U121" s="6"/>
     </row>
     <row r="122" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="64"/>
+      <c r="A122" s="67"/>
       <c r="B122" s="39" t="s">
         <v>165</v>
       </c>
@@ -6048,7 +6048,7 @@
       <c r="U122" s="6"/>
     </row>
     <row r="123" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="71">
+      <c r="A123" s="63">
         <v>18</v>
       </c>
       <c r="B123" s="35" t="s">
@@ -6081,7 +6081,7 @@
       <c r="U123" s="14"/>
     </row>
     <row r="124" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="71"/>
+      <c r="A124" s="63"/>
       <c r="B124" s="35" t="s">
         <v>167</v>
       </c>
@@ -6112,7 +6112,7 @@
       <c r="U124" s="14"/>
     </row>
     <row r="125" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="71"/>
+      <c r="A125" s="63"/>
       <c r="B125" s="35" t="s">
         <v>168</v>
       </c>
@@ -6143,7 +6143,7 @@
       <c r="U125" s="14"/>
     </row>
     <row r="126" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="71"/>
+      <c r="A126" s="63"/>
       <c r="B126" s="35" t="s">
         <v>169</v>
       </c>
@@ -6174,36 +6174,36 @@
       <c r="U126" s="14"/>
     </row>
     <row r="127" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="71"/>
+      <c r="A127" s="63"/>
       <c r="B127" s="34" t="s">
         <v>170</v>
       </c>
       <c r="C127" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="D127" s="77" t="s">
+      <c r="D127" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="E127" s="78"/>
-      <c r="F127" s="78"/>
-      <c r="G127" s="78"/>
-      <c r="H127" s="78"/>
-      <c r="I127" s="78"/>
-      <c r="J127" s="78"/>
-      <c r="K127" s="78"/>
-      <c r="L127" s="78"/>
-      <c r="M127" s="78"/>
-      <c r="N127" s="78"/>
-      <c r="O127" s="78"/>
-      <c r="P127" s="78"/>
-      <c r="Q127" s="78"/>
-      <c r="R127" s="78"/>
-      <c r="S127" s="78"/>
-      <c r="T127" s="78"/>
-      <c r="U127" s="79"/>
+      <c r="E127" s="65"/>
+      <c r="F127" s="65"/>
+      <c r="G127" s="65"/>
+      <c r="H127" s="65"/>
+      <c r="I127" s="65"/>
+      <c r="J127" s="65"/>
+      <c r="K127" s="65"/>
+      <c r="L127" s="65"/>
+      <c r="M127" s="65"/>
+      <c r="N127" s="65"/>
+      <c r="O127" s="65"/>
+      <c r="P127" s="65"/>
+      <c r="Q127" s="65"/>
+      <c r="R127" s="65"/>
+      <c r="S127" s="65"/>
+      <c r="T127" s="65"/>
+      <c r="U127" s="66"/>
     </row>
     <row r="128" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="71"/>
+      <c r="A128" s="63"/>
       <c r="B128" s="35" t="s">
         <v>171</v>
       </c>
@@ -6234,7 +6234,7 @@
       <c r="U128" s="14"/>
     </row>
     <row r="129" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="71"/>
+      <c r="A129" s="63"/>
       <c r="B129" s="35" t="s">
         <v>172</v>
       </c>
@@ -6265,7 +6265,7 @@
       <c r="U129" s="14"/>
     </row>
     <row r="130" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A130" s="64">
+      <c r="A130" s="67">
         <v>19</v>
       </c>
       <c r="B130" s="39" t="s">
@@ -6298,7 +6298,7 @@
       <c r="U130" s="6"/>
     </row>
     <row r="131" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A131" s="64"/>
+      <c r="A131" s="67"/>
       <c r="B131" s="39" t="s">
         <v>174</v>
       </c>
@@ -6329,7 +6329,7 @@
       <c r="U131" s="6"/>
     </row>
     <row r="132" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A132" s="64"/>
+      <c r="A132" s="67"/>
       <c r="B132" s="39" t="s">
         <v>175</v>
       </c>
@@ -6360,7 +6360,7 @@
       <c r="U132" s="6"/>
     </row>
     <row r="133" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A133" s="64"/>
+      <c r="A133" s="67"/>
       <c r="B133" s="39" t="s">
         <v>176</v>
       </c>
@@ -6391,7 +6391,7 @@
       <c r="U133" s="6"/>
     </row>
     <row r="134" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A134" s="64"/>
+      <c r="A134" s="67"/>
       <c r="B134" s="39" t="s">
         <v>177</v>
       </c>
@@ -6422,7 +6422,7 @@
       <c r="U134" s="6"/>
     </row>
     <row r="135" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A135" s="64"/>
+      <c r="A135" s="67"/>
       <c r="B135" s="39" t="s">
         <v>178</v>
       </c>
@@ -6453,7 +6453,7 @@
       <c r="U135" s="6"/>
     </row>
     <row r="136" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A136" s="64"/>
+      <c r="A136" s="67"/>
       <c r="B136" s="39" t="s">
         <v>179</v>
       </c>
@@ -6499,28 +6499,6 @@
     <row r="150" ht="20.25"/>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A123:A129"/>
-    <mergeCell ref="D127:U127"/>
-    <mergeCell ref="A130:A136"/>
-    <mergeCell ref="D81:U94"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A102:A108"/>
-    <mergeCell ref="A109:A115"/>
-    <mergeCell ref="A116:A122"/>
-    <mergeCell ref="A81:A87"/>
-    <mergeCell ref="A46:A52"/>
-    <mergeCell ref="A53:A59"/>
-    <mergeCell ref="A60:A66"/>
-    <mergeCell ref="A67:A73"/>
-    <mergeCell ref="A74:A80"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="D29:U31"/>
-    <mergeCell ref="M2:O2"/>
     <mergeCell ref="A32:A38"/>
     <mergeCell ref="D35:U41"/>
     <mergeCell ref="A39:A45"/>
@@ -6536,6 +6514,28 @@
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="D29:U31"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="A46:A52"/>
+    <mergeCell ref="A53:A59"/>
+    <mergeCell ref="A60:A66"/>
+    <mergeCell ref="A67:A73"/>
+    <mergeCell ref="A74:A80"/>
+    <mergeCell ref="A123:A129"/>
+    <mergeCell ref="D127:U127"/>
+    <mergeCell ref="A130:A136"/>
+    <mergeCell ref="D81:U94"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="A95:A101"/>
+    <mergeCell ref="A102:A108"/>
+    <mergeCell ref="A109:A115"/>
+    <mergeCell ref="A116:A122"/>
+    <mergeCell ref="A81:A87"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6578,81 +6578,81 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="73" t="s">
+      <c r="B2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="74"/>
-      <c r="D2" s="63" t="s">
+      <c r="C2" s="89"/>
+      <c r="D2" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63" t="s">
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="63" t="s">
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="63"/>
-      <c r="L2" s="63"/>
-      <c r="M2" s="63" t="s">
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="63"/>
-      <c r="O2" s="63"/>
-      <c r="P2" s="63" t="s">
+      <c r="N2" s="77"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="63"/>
-      <c r="R2" s="63"/>
-      <c r="S2" s="63" t="s">
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="63"/>
-      <c r="U2" s="63"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
     </row>
     <row r="3" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="72" t="s">
+      <c r="A3" s="77"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="87" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="63" t="s">
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63" t="s">
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="63"/>
-      <c r="L3" s="63"/>
-      <c r="M3" s="63" t="s">
+      <c r="K3" s="77"/>
+      <c r="L3" s="77"/>
+      <c r="M3" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="63"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63" t="s">
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="64">
+      <c r="A4" s="67">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -6710,7 +6710,7 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="64"/>
+      <c r="A5" s="67"/>
       <c r="B5" s="2" t="s">
         <v>23</v>
       </c>
@@ -6774,7 +6774,7 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="64"/>
+      <c r="A6" s="67"/>
       <c r="B6" s="2" t="s">
         <v>27</v>
       </c>
@@ -6820,7 +6820,7 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="64"/>
+      <c r="A7" s="67"/>
       <c r="B7" s="2" t="s">
         <v>29</v>
       </c>
@@ -6864,7 +6864,7 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="64"/>
+      <c r="A8" s="67"/>
       <c r="B8" s="2" t="s">
         <v>32</v>
       </c>
@@ -6928,7 +6928,7 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="64"/>
+      <c r="A9" s="67"/>
       <c r="B9" s="2" t="s">
         <v>37</v>
       </c>
@@ -6970,7 +6970,7 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="64"/>
+      <c r="A10" s="67"/>
       <c r="B10" s="2" t="s">
         <v>40</v>
       </c>
@@ -7014,7 +7014,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="71">
+      <c r="A11" s="63">
         <v>2</v>
       </c>
       <c r="B11" s="11" t="s">
@@ -7078,7 +7078,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="71"/>
+      <c r="A12" s="63"/>
       <c r="B12" s="11" t="s">
         <v>46</v>
       </c>
@@ -7140,7 +7140,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="71"/>
+      <c r="A13" s="63"/>
       <c r="B13" s="11" t="s">
         <v>48</v>
       </c>
@@ -7192,7 +7192,7 @@
       <c r="AA13" s="10"/>
     </row>
     <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="71"/>
+      <c r="A14" s="63"/>
       <c r="B14" s="11" t="s">
         <v>49</v>
       </c>
@@ -7238,7 +7238,7 @@
       <c r="AA14" s="10"/>
     </row>
     <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="71"/>
+      <c r="A15" s="63"/>
       <c r="B15" s="11" t="s">
         <v>53</v>
       </c>
@@ -7290,7 +7290,7 @@
       <c r="AA15" s="10"/>
     </row>
     <row r="16" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="71"/>
+      <c r="A16" s="63"/>
       <c r="B16" s="11" t="s">
         <v>54</v>
       </c>
@@ -7317,7 +7317,7 @@
       <c r="U16" s="15"/>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="71"/>
+      <c r="A17" s="63"/>
       <c r="B17" s="11" t="s">
         <v>55</v>
       </c>
@@ -7344,7 +7344,7 @@
       <c r="U17" s="15"/>
     </row>
     <row r="18" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="64">
+      <c r="A18" s="67">
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -7393,7 +7393,7 @@
       <c r="U18" s="6"/>
     </row>
     <row r="19" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="64"/>
+      <c r="A19" s="67"/>
       <c r="B19" s="2" t="s">
         <v>57</v>
       </c>
@@ -7440,7 +7440,7 @@
       <c r="U19" s="6"/>
     </row>
     <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="64"/>
+      <c r="A20" s="67"/>
       <c r="B20" s="2" t="s">
         <v>58</v>
       </c>
@@ -7469,7 +7469,7 @@
       <c r="U20" s="6"/>
     </row>
     <row r="21" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="64"/>
+      <c r="A21" s="67"/>
       <c r="B21" s="2" t="s">
         <v>60</v>
       </c>
@@ -7528,7 +7528,7 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="64"/>
+      <c r="A22" s="67"/>
       <c r="B22" s="2" t="s">
         <v>61</v>
       </c>
@@ -7575,7 +7575,7 @@
       <c r="U22" s="6"/>
     </row>
     <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="64"/>
+      <c r="A23" s="67"/>
       <c r="B23" s="2" t="s">
         <v>62</v>
       </c>
@@ -7602,7 +7602,7 @@
       <c r="U23" s="6"/>
     </row>
     <row r="24" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="64"/>
+      <c r="A24" s="67"/>
       <c r="B24" s="19" t="s">
         <v>63</v>
       </c>
@@ -7629,7 +7629,7 @@
       <c r="U24" s="26"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="71">
+      <c r="A25" s="63">
         <v>4</v>
       </c>
       <c r="B25" s="11" t="s">
@@ -7678,7 +7678,7 @@
       <c r="U25" s="15"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="71"/>
+      <c r="A26" s="63"/>
       <c r="B26" s="11" t="s">
         <v>65</v>
       </c>
@@ -7725,7 +7725,7 @@
       <c r="U26" s="15"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="71"/>
+      <c r="A27" s="63"/>
       <c r="B27" s="11" t="s">
         <v>66</v>
       </c>
@@ -7772,7 +7772,7 @@
       <c r="U27" s="15"/>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="71"/>
+      <c r="A28" s="63"/>
       <c r="B28" s="11" t="s">
         <v>67</v>
       </c>
@@ -7819,90 +7819,90 @@
       <c r="U28" s="15"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="71"/>
+      <c r="A29" s="63"/>
       <c r="B29" s="32" t="s">
         <v>68</v>
       </c>
       <c r="C29" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="D29" s="86" t="s">
+      <c r="D29" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="E29" s="65"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
-      <c r="H29" s="65"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="65"/>
-      <c r="K29" s="65"/>
-      <c r="L29" s="65"/>
-      <c r="M29" s="65"/>
-      <c r="N29" s="65"/>
-      <c r="O29" s="65"/>
-      <c r="P29" s="65"/>
-      <c r="Q29" s="65"/>
-      <c r="R29" s="65"/>
-      <c r="S29" s="65"/>
-      <c r="T29" s="65"/>
-      <c r="U29" s="66"/>
+      <c r="E29" s="79"/>
+      <c r="F29" s="79"/>
+      <c r="G29" s="79"/>
+      <c r="H29" s="79"/>
+      <c r="I29" s="79"/>
+      <c r="J29" s="79"/>
+      <c r="K29" s="79"/>
+      <c r="L29" s="79"/>
+      <c r="M29" s="79"/>
+      <c r="N29" s="79"/>
+      <c r="O29" s="79"/>
+      <c r="P29" s="79"/>
+      <c r="Q29" s="79"/>
+      <c r="R29" s="79"/>
+      <c r="S29" s="79"/>
+      <c r="T29" s="79"/>
+      <c r="U29" s="80"/>
     </row>
     <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="71"/>
+      <c r="A30" s="63"/>
       <c r="B30" s="32" t="s">
         <v>70</v>
       </c>
       <c r="C30" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="D30" s="87"/>
-      <c r="E30" s="67"/>
-      <c r="F30" s="67"/>
-      <c r="G30" s="67"/>
-      <c r="H30" s="67"/>
-      <c r="I30" s="67"/>
-      <c r="J30" s="67"/>
-      <c r="K30" s="67"/>
-      <c r="L30" s="67"/>
-      <c r="M30" s="67"/>
-      <c r="N30" s="67"/>
-      <c r="O30" s="67"/>
-      <c r="P30" s="67"/>
-      <c r="Q30" s="67"/>
-      <c r="R30" s="67"/>
-      <c r="S30" s="67"/>
-      <c r="T30" s="67"/>
-      <c r="U30" s="68"/>
+      <c r="D30" s="81"/>
+      <c r="E30" s="82"/>
+      <c r="F30" s="82"/>
+      <c r="G30" s="82"/>
+      <c r="H30" s="82"/>
+      <c r="I30" s="82"/>
+      <c r="J30" s="82"/>
+      <c r="K30" s="82"/>
+      <c r="L30" s="82"/>
+      <c r="M30" s="82"/>
+      <c r="N30" s="82"/>
+      <c r="O30" s="82"/>
+      <c r="P30" s="82"/>
+      <c r="Q30" s="82"/>
+      <c r="R30" s="82"/>
+      <c r="S30" s="82"/>
+      <c r="T30" s="82"/>
+      <c r="U30" s="83"/>
     </row>
     <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="71"/>
+      <c r="A31" s="63"/>
       <c r="B31" s="32" t="s">
         <v>71</v>
       </c>
       <c r="C31" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="88"/>
-      <c r="E31" s="69"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="69"/>
-      <c r="H31" s="69"/>
-      <c r="I31" s="69"/>
-      <c r="J31" s="69"/>
-      <c r="K31" s="69"/>
-      <c r="L31" s="69"/>
-      <c r="M31" s="69"/>
-      <c r="N31" s="69"/>
-      <c r="O31" s="69"/>
-      <c r="P31" s="69"/>
-      <c r="Q31" s="69"/>
-      <c r="R31" s="69"/>
-      <c r="S31" s="69"/>
-      <c r="T31" s="69"/>
-      <c r="U31" s="70"/>
+      <c r="D31" s="84"/>
+      <c r="E31" s="85"/>
+      <c r="F31" s="85"/>
+      <c r="G31" s="85"/>
+      <c r="H31" s="85"/>
+      <c r="I31" s="85"/>
+      <c r="J31" s="85"/>
+      <c r="K31" s="85"/>
+      <c r="L31" s="85"/>
+      <c r="M31" s="85"/>
+      <c r="N31" s="85"/>
+      <c r="O31" s="85"/>
+      <c r="P31" s="85"/>
+      <c r="Q31" s="85"/>
+      <c r="R31" s="85"/>
+      <c r="S31" s="85"/>
+      <c r="T31" s="85"/>
+      <c r="U31" s="86"/>
     </row>
     <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="64">
+      <c r="A32" s="67">
         <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -7951,7 +7951,7 @@
       <c r="U32" s="6"/>
     </row>
     <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="64"/>
+      <c r="A33" s="67"/>
       <c r="B33" s="2" t="s">
         <v>73</v>
       </c>
@@ -7998,7 +7998,7 @@
       <c r="U33" s="6"/>
     </row>
     <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="64"/>
+      <c r="A34" s="67"/>
       <c r="B34" s="2" t="s">
         <v>74</v>
       </c>
@@ -8045,117 +8045,117 @@
       <c r="U34" s="6"/>
     </row>
     <row r="35" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="64"/>
+      <c r="A35" s="67"/>
       <c r="B35" s="34" t="s">
         <v>75</v>
       </c>
       <c r="C35" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="86" t="s">
+      <c r="D35" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="E35" s="65"/>
-      <c r="F35" s="65"/>
-      <c r="G35" s="65"/>
-      <c r="H35" s="65"/>
-      <c r="I35" s="65"/>
-      <c r="J35" s="65"/>
-      <c r="K35" s="65"/>
-      <c r="L35" s="65"/>
-      <c r="M35" s="65"/>
-      <c r="N35" s="65"/>
-      <c r="O35" s="65"/>
-      <c r="P35" s="65"/>
-      <c r="Q35" s="65"/>
-      <c r="R35" s="65"/>
-      <c r="S35" s="65"/>
-      <c r="T35" s="65"/>
-      <c r="U35" s="66"/>
+      <c r="E35" s="79"/>
+      <c r="F35" s="79"/>
+      <c r="G35" s="79"/>
+      <c r="H35" s="79"/>
+      <c r="I35" s="79"/>
+      <c r="J35" s="79"/>
+      <c r="K35" s="79"/>
+      <c r="L35" s="79"/>
+      <c r="M35" s="79"/>
+      <c r="N35" s="79"/>
+      <c r="O35" s="79"/>
+      <c r="P35" s="79"/>
+      <c r="Q35" s="79"/>
+      <c r="R35" s="79"/>
+      <c r="S35" s="79"/>
+      <c r="T35" s="79"/>
+      <c r="U35" s="80"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="64"/>
+      <c r="A36" s="67"/>
       <c r="B36" s="34" t="s">
         <v>76</v>
       </c>
       <c r="C36" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="D36" s="87"/>
-      <c r="E36" s="67"/>
-      <c r="F36" s="67"/>
-      <c r="G36" s="67"/>
-      <c r="H36" s="67"/>
-      <c r="I36" s="67"/>
-      <c r="J36" s="67"/>
-      <c r="K36" s="67"/>
-      <c r="L36" s="67"/>
-      <c r="M36" s="67"/>
-      <c r="N36" s="67"/>
-      <c r="O36" s="67"/>
-      <c r="P36" s="67"/>
-      <c r="Q36" s="67"/>
-      <c r="R36" s="67"/>
-      <c r="S36" s="67"/>
-      <c r="T36" s="67"/>
-      <c r="U36" s="68"/>
+      <c r="D36" s="81"/>
+      <c r="E36" s="82"/>
+      <c r="F36" s="82"/>
+      <c r="G36" s="82"/>
+      <c r="H36" s="82"/>
+      <c r="I36" s="82"/>
+      <c r="J36" s="82"/>
+      <c r="K36" s="82"/>
+      <c r="L36" s="82"/>
+      <c r="M36" s="82"/>
+      <c r="N36" s="82"/>
+      <c r="O36" s="82"/>
+      <c r="P36" s="82"/>
+      <c r="Q36" s="82"/>
+      <c r="R36" s="82"/>
+      <c r="S36" s="82"/>
+      <c r="T36" s="82"/>
+      <c r="U36" s="83"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="64"/>
+      <c r="A37" s="67"/>
       <c r="B37" s="34" t="s">
         <v>77</v>
       </c>
       <c r="C37" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="D37" s="87"/>
-      <c r="E37" s="67"/>
-      <c r="F37" s="67"/>
-      <c r="G37" s="67"/>
-      <c r="H37" s="67"/>
-      <c r="I37" s="67"/>
-      <c r="J37" s="67"/>
-      <c r="K37" s="67"/>
-      <c r="L37" s="67"/>
-      <c r="M37" s="67"/>
-      <c r="N37" s="67"/>
-      <c r="O37" s="67"/>
-      <c r="P37" s="67"/>
-      <c r="Q37" s="67"/>
-      <c r="R37" s="67"/>
-      <c r="S37" s="67"/>
-      <c r="T37" s="67"/>
-      <c r="U37" s="68"/>
+      <c r="D37" s="81"/>
+      <c r="E37" s="82"/>
+      <c r="F37" s="82"/>
+      <c r="G37" s="82"/>
+      <c r="H37" s="82"/>
+      <c r="I37" s="82"/>
+      <c r="J37" s="82"/>
+      <c r="K37" s="82"/>
+      <c r="L37" s="82"/>
+      <c r="M37" s="82"/>
+      <c r="N37" s="82"/>
+      <c r="O37" s="82"/>
+      <c r="P37" s="82"/>
+      <c r="Q37" s="82"/>
+      <c r="R37" s="82"/>
+      <c r="S37" s="82"/>
+      <c r="T37" s="82"/>
+      <c r="U37" s="83"/>
     </row>
     <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="64"/>
+      <c r="A38" s="67"/>
       <c r="B38" s="34" t="s">
         <v>78</v>
       </c>
       <c r="C38" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="D38" s="87"/>
-      <c r="E38" s="67"/>
-      <c r="F38" s="67"/>
-      <c r="G38" s="67"/>
-      <c r="H38" s="67"/>
-      <c r="I38" s="67"/>
-      <c r="J38" s="67"/>
-      <c r="K38" s="67"/>
-      <c r="L38" s="67"/>
-      <c r="M38" s="67"/>
-      <c r="N38" s="67"/>
-      <c r="O38" s="67"/>
-      <c r="P38" s="67"/>
-      <c r="Q38" s="67"/>
-      <c r="R38" s="67"/>
-      <c r="S38" s="67"/>
-      <c r="T38" s="67"/>
-      <c r="U38" s="68"/>
+      <c r="D38" s="81"/>
+      <c r="E38" s="82"/>
+      <c r="F38" s="82"/>
+      <c r="G38" s="82"/>
+      <c r="H38" s="82"/>
+      <c r="I38" s="82"/>
+      <c r="J38" s="82"/>
+      <c r="K38" s="82"/>
+      <c r="L38" s="82"/>
+      <c r="M38" s="82"/>
+      <c r="N38" s="82"/>
+      <c r="O38" s="82"/>
+      <c r="P38" s="82"/>
+      <c r="Q38" s="82"/>
+      <c r="R38" s="82"/>
+      <c r="S38" s="82"/>
+      <c r="T38" s="82"/>
+      <c r="U38" s="83"/>
     </row>
     <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="71">
+      <c r="A39" s="63">
         <v>6</v>
       </c>
       <c r="B39" s="34" t="s">
@@ -8164,81 +8164,81 @@
       <c r="C39" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="87"/>
-      <c r="E39" s="67"/>
-      <c r="F39" s="67"/>
-      <c r="G39" s="67"/>
-      <c r="H39" s="67"/>
-      <c r="I39" s="67"/>
-      <c r="J39" s="67"/>
-      <c r="K39" s="67"/>
-      <c r="L39" s="67"/>
-      <c r="M39" s="67"/>
-      <c r="N39" s="67"/>
-      <c r="O39" s="67"/>
-      <c r="P39" s="67"/>
-      <c r="Q39" s="67"/>
-      <c r="R39" s="67"/>
-      <c r="S39" s="67"/>
-      <c r="T39" s="67"/>
-      <c r="U39" s="68"/>
+      <c r="D39" s="81"/>
+      <c r="E39" s="82"/>
+      <c r="F39" s="82"/>
+      <c r="G39" s="82"/>
+      <c r="H39" s="82"/>
+      <c r="I39" s="82"/>
+      <c r="J39" s="82"/>
+      <c r="K39" s="82"/>
+      <c r="L39" s="82"/>
+      <c r="M39" s="82"/>
+      <c r="N39" s="82"/>
+      <c r="O39" s="82"/>
+      <c r="P39" s="82"/>
+      <c r="Q39" s="82"/>
+      <c r="R39" s="82"/>
+      <c r="S39" s="82"/>
+      <c r="T39" s="82"/>
+      <c r="U39" s="83"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="71"/>
+      <c r="A40" s="63"/>
       <c r="B40" s="34" t="s">
         <v>80</v>
       </c>
       <c r="C40" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="D40" s="87"/>
-      <c r="E40" s="67"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="67"/>
-      <c r="H40" s="67"/>
-      <c r="I40" s="67"/>
-      <c r="J40" s="67"/>
-      <c r="K40" s="67"/>
-      <c r="L40" s="67"/>
-      <c r="M40" s="67"/>
-      <c r="N40" s="67"/>
-      <c r="O40" s="67"/>
-      <c r="P40" s="67"/>
-      <c r="Q40" s="67"/>
-      <c r="R40" s="67"/>
-      <c r="S40" s="67"/>
-      <c r="T40" s="67"/>
-      <c r="U40" s="68"/>
+      <c r="D40" s="81"/>
+      <c r="E40" s="82"/>
+      <c r="F40" s="82"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="82"/>
+      <c r="I40" s="82"/>
+      <c r="J40" s="82"/>
+      <c r="K40" s="82"/>
+      <c r="L40" s="82"/>
+      <c r="M40" s="82"/>
+      <c r="N40" s="82"/>
+      <c r="O40" s="82"/>
+      <c r="P40" s="82"/>
+      <c r="Q40" s="82"/>
+      <c r="R40" s="82"/>
+      <c r="S40" s="82"/>
+      <c r="T40" s="82"/>
+      <c r="U40" s="83"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="71"/>
+      <c r="A41" s="63"/>
       <c r="B41" s="34" t="s">
         <v>81</v>
       </c>
       <c r="C41" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="D41" s="88"/>
-      <c r="E41" s="69"/>
-      <c r="F41" s="69"/>
-      <c r="G41" s="69"/>
-      <c r="H41" s="69"/>
-      <c r="I41" s="69"/>
-      <c r="J41" s="69"/>
-      <c r="K41" s="69"/>
-      <c r="L41" s="69"/>
-      <c r="M41" s="69"/>
-      <c r="N41" s="69"/>
-      <c r="O41" s="69"/>
-      <c r="P41" s="69"/>
-      <c r="Q41" s="69"/>
-      <c r="R41" s="69"/>
-      <c r="S41" s="69"/>
-      <c r="T41" s="69"/>
-      <c r="U41" s="70"/>
+      <c r="D41" s="84"/>
+      <c r="E41" s="85"/>
+      <c r="F41" s="85"/>
+      <c r="G41" s="85"/>
+      <c r="H41" s="85"/>
+      <c r="I41" s="85"/>
+      <c r="J41" s="85"/>
+      <c r="K41" s="85"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="85"/>
+      <c r="N41" s="85"/>
+      <c r="O41" s="85"/>
+      <c r="P41" s="85"/>
+      <c r="Q41" s="85"/>
+      <c r="R41" s="85"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="85"/>
+      <c r="U41" s="86"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="71"/>
+      <c r="A42" s="63"/>
       <c r="B42" s="35" t="s">
         <v>82</v>
       </c>
@@ -8297,7 +8297,7 @@
       </c>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="71"/>
+      <c r="A43" s="63"/>
       <c r="B43" s="35" t="s">
         <v>83</v>
       </c>
@@ -8326,7 +8326,7 @@
       <c r="U43" s="15"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="71"/>
+      <c r="A44" s="63"/>
       <c r="B44" s="37" t="s">
         <v>84</v>
       </c>
@@ -8371,7 +8371,7 @@
       <c r="U44" s="26"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="71"/>
+      <c r="A45" s="63"/>
       <c r="B45" s="35" t="s">
         <v>86</v>
       </c>
@@ -8398,7 +8398,7 @@
       <c r="U45" s="15"/>
     </row>
     <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="64">
+      <c r="A46" s="67">
         <v>7</v>
       </c>
       <c r="B46" s="39" t="s">
@@ -8447,7 +8447,7 @@
       <c r="U46" s="6"/>
     </row>
     <row r="47" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="64"/>
+      <c r="A47" s="67"/>
       <c r="B47" s="39" t="s">
         <v>88</v>
       </c>
@@ -8494,7 +8494,7 @@
       <c r="U47" s="6"/>
     </row>
     <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="64"/>
+      <c r="A48" s="67"/>
       <c r="B48" s="39" t="s">
         <v>89</v>
       </c>
@@ -8523,7 +8523,7 @@
       <c r="U48" s="6"/>
     </row>
     <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="64"/>
+      <c r="A49" s="67"/>
       <c r="B49" s="39" t="s">
         <v>90</v>
       </c>
@@ -8570,7 +8570,7 @@
       <c r="U49" s="6"/>
     </row>
     <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="64"/>
+      <c r="A50" s="67"/>
       <c r="B50" s="39" t="s">
         <v>91</v>
       </c>
@@ -8599,7 +8599,7 @@
       <c r="U50" s="6"/>
     </row>
     <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="64"/>
+      <c r="A51" s="67"/>
       <c r="B51" s="39" t="s">
         <v>92</v>
       </c>
@@ -8626,7 +8626,7 @@
       <c r="U51" s="6"/>
     </row>
     <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="64"/>
+      <c r="A52" s="67"/>
       <c r="B52" s="39" t="s">
         <v>93</v>
       </c>
@@ -8653,7 +8653,7 @@
       <c r="U52" s="6"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="71">
+      <c r="A53" s="63">
         <v>8</v>
       </c>
       <c r="B53" s="35" t="s">
@@ -8702,7 +8702,7 @@
       <c r="U53" s="15"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="71"/>
+      <c r="A54" s="63"/>
       <c r="B54" s="35" t="s">
         <v>95</v>
       </c>
@@ -8749,7 +8749,7 @@
       <c r="U54" s="15"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="71"/>
+      <c r="A55" s="63"/>
       <c r="B55" s="35" t="s">
         <v>96</v>
       </c>
@@ -8796,7 +8796,7 @@
       <c r="U55" s="15"/>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="71"/>
+      <c r="A56" s="63"/>
       <c r="B56" s="35" t="s">
         <v>97</v>
       </c>
@@ -8855,7 +8855,7 @@
       </c>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="71"/>
+      <c r="A57" s="63"/>
       <c r="B57" s="35" t="s">
         <v>98</v>
       </c>
@@ -8902,7 +8902,7 @@
       <c r="U57" s="15"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="71"/>
+      <c r="A58" s="63"/>
       <c r="B58" s="35" t="s">
         <v>99</v>
       </c>
@@ -8912,33 +8912,15 @@
       <c r="D58" s="11"/>
       <c r="E58" s="13"/>
       <c r="F58" s="14"/>
-      <c r="G58" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="H58" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="I58" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="J58" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K58" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="L58" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="M58" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="N58" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="O58" s="15" t="s">
-        <v>85</v>
-      </c>
+      <c r="G58" s="11"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="15"/>
+      <c r="J58" s="11"/>
+      <c r="K58" s="13"/>
+      <c r="L58" s="15"/>
+      <c r="M58" s="11"/>
+      <c r="N58" s="13"/>
+      <c r="O58" s="15"/>
       <c r="P58" s="11"/>
       <c r="Q58" s="13"/>
       <c r="R58" s="15"/>
@@ -8947,7 +8929,7 @@
       <c r="U58" s="15"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="71"/>
+      <c r="A59" s="63"/>
       <c r="B59" s="35" t="s">
         <v>100</v>
       </c>
@@ -8974,7 +8956,7 @@
       <c r="U59" s="15"/>
     </row>
     <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="64">
+      <c r="A60" s="67">
         <v>9</v>
       </c>
       <c r="B60" s="39" t="s">
@@ -9023,7 +9005,7 @@
       <c r="U60" s="6"/>
     </row>
     <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="64"/>
+      <c r="A61" s="67"/>
       <c r="B61" s="39" t="s">
         <v>102</v>
       </c>
@@ -9070,7 +9052,7 @@
       <c r="U61" s="6"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="64"/>
+      <c r="A62" s="67"/>
       <c r="B62" s="39" t="s">
         <v>103</v>
       </c>
@@ -9117,7 +9099,7 @@
       <c r="U62" s="6"/>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="64"/>
+      <c r="A63" s="67"/>
       <c r="B63" s="39" t="s">
         <v>104</v>
       </c>
@@ -9176,7 +9158,7 @@
       </c>
     </row>
     <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="64"/>
+      <c r="A64" s="67"/>
       <c r="B64" s="39" t="s">
         <v>105</v>
       </c>
@@ -9223,7 +9205,7 @@
       <c r="U64" s="5"/>
     </row>
     <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="64"/>
+      <c r="A65" s="67"/>
       <c r="B65" s="39" t="s">
         <v>106</v>
       </c>
@@ -9250,7 +9232,7 @@
       <c r="U65" s="5"/>
     </row>
     <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="64"/>
+      <c r="A66" s="67"/>
       <c r="B66" s="39" t="s">
         <v>107</v>
       </c>
@@ -9277,7 +9259,7 @@
       <c r="U66" s="5"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="71">
+      <c r="A67" s="63">
         <v>10</v>
       </c>
       <c r="B67" s="35" t="s">
@@ -9326,7 +9308,7 @@
       <c r="U67" s="14"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="71"/>
+      <c r="A68" s="63"/>
       <c r="B68" s="35" t="s">
         <v>109</v>
       </c>
@@ -9373,7 +9355,7 @@
       <c r="U68" s="14"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="71"/>
+      <c r="A69" s="63"/>
       <c r="B69" s="35" t="s">
         <v>110</v>
       </c>
@@ -9402,7 +9384,7 @@
       <c r="U69" s="14"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="71"/>
+      <c r="A70" s="63"/>
       <c r="B70" s="35" t="s">
         <v>111</v>
       </c>
@@ -9461,7 +9443,7 @@
       </c>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="71"/>
+      <c r="A71" s="63"/>
       <c r="B71" s="35" t="s">
         <v>112</v>
       </c>
@@ -9490,7 +9472,7 @@
       <c r="U71" s="14"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="71"/>
+      <c r="A72" s="63"/>
       <c r="B72" s="35" t="s">
         <v>113</v>
       </c>
@@ -9500,15 +9482,33 @@
       <c r="D72" s="11"/>
       <c r="E72" s="13"/>
       <c r="F72" s="14"/>
-      <c r="G72" s="11"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="15"/>
-      <c r="J72" s="11"/>
-      <c r="K72" s="13"/>
-      <c r="L72" s="15"/>
-      <c r="M72" s="11"/>
-      <c r="N72" s="13"/>
-      <c r="O72" s="15"/>
+      <c r="G72" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H72" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="I72" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="J72" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="K72" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="L72" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="M72" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N72" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="O72" s="15" t="s">
+        <v>85</v>
+      </c>
       <c r="P72" s="11"/>
       <c r="Q72" s="13"/>
       <c r="R72" s="14"/>
@@ -9517,7 +9517,7 @@
       <c r="U72" s="14"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="71"/>
+      <c r="A73" s="63"/>
       <c r="B73" s="35" t="s">
         <v>114</v>
       </c>
@@ -9544,7 +9544,7 @@
       <c r="U73" s="14"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="64">
+      <c r="A74" s="67">
         <v>11</v>
       </c>
       <c r="B74" s="39" t="s">
@@ -9593,7 +9593,7 @@
       <c r="U74" s="5"/>
     </row>
     <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A75" s="64"/>
+      <c r="A75" s="67"/>
       <c r="B75" s="39" t="s">
         <v>116</v>
       </c>
@@ -9640,7 +9640,7 @@
       <c r="U75" s="5"/>
     </row>
     <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A76" s="64"/>
+      <c r="A76" s="67"/>
       <c r="B76" s="39" t="s">
         <v>117</v>
       </c>
@@ -9669,7 +9669,7 @@
       <c r="U76" s="5"/>
     </row>
     <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A77" s="64"/>
+      <c r="A77" s="67"/>
       <c r="B77" s="39" t="s">
         <v>118</v>
       </c>
@@ -9716,7 +9716,7 @@
       <c r="U77" s="6"/>
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A78" s="64"/>
+      <c r="A78" s="67"/>
       <c r="B78" s="39" t="s">
         <v>119</v>
       </c>
@@ -9745,7 +9745,7 @@
       <c r="U78" s="6"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A79" s="64"/>
+      <c r="A79" s="67"/>
       <c r="B79" s="39" t="s">
         <v>120</v>
       </c>
@@ -9772,7 +9772,7 @@
       <c r="U79" s="6"/>
     </row>
     <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A80" s="64"/>
+      <c r="A80" s="67"/>
       <c r="B80" s="39" t="s">
         <v>121</v>
       </c>
@@ -9799,7 +9799,7 @@
       <c r="U80" s="6"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="71">
+      <c r="A81" s="63">
         <v>12</v>
       </c>
       <c r="B81" s="35" t="s">
@@ -9808,191 +9808,191 @@
       <c r="C81" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="D81" s="89" t="s">
+      <c r="D81" s="68" t="s">
         <v>123</v>
       </c>
-      <c r="E81" s="80"/>
-      <c r="F81" s="80"/>
-      <c r="G81" s="80"/>
-      <c r="H81" s="80"/>
-      <c r="I81" s="80"/>
-      <c r="J81" s="80"/>
-      <c r="K81" s="80"/>
-      <c r="L81" s="80"/>
-      <c r="M81" s="80"/>
-      <c r="N81" s="80"/>
-      <c r="O81" s="80"/>
-      <c r="P81" s="80"/>
-      <c r="Q81" s="80"/>
-      <c r="R81" s="80"/>
-      <c r="S81" s="80"/>
-      <c r="T81" s="80"/>
-      <c r="U81" s="81"/>
+      <c r="E81" s="69"/>
+      <c r="F81" s="69"/>
+      <c r="G81" s="69"/>
+      <c r="H81" s="69"/>
+      <c r="I81" s="69"/>
+      <c r="J81" s="69"/>
+      <c r="K81" s="69"/>
+      <c r="L81" s="69"/>
+      <c r="M81" s="69"/>
+      <c r="N81" s="69"/>
+      <c r="O81" s="69"/>
+      <c r="P81" s="69"/>
+      <c r="Q81" s="69"/>
+      <c r="R81" s="69"/>
+      <c r="S81" s="69"/>
+      <c r="T81" s="69"/>
+      <c r="U81" s="70"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="71"/>
+      <c r="A82" s="63"/>
       <c r="B82" s="35" t="s">
         <v>124</v>
       </c>
       <c r="C82" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="D82" s="90"/>
-      <c r="E82" s="82"/>
-      <c r="F82" s="82"/>
-      <c r="G82" s="82"/>
-      <c r="H82" s="82"/>
-      <c r="I82" s="82"/>
-      <c r="J82" s="82"/>
-      <c r="K82" s="82"/>
-      <c r="L82" s="82"/>
-      <c r="M82" s="82"/>
-      <c r="N82" s="82"/>
-      <c r="O82" s="82"/>
-      <c r="P82" s="82"/>
-      <c r="Q82" s="82"/>
-      <c r="R82" s="82"/>
-      <c r="S82" s="82"/>
-      <c r="T82" s="82"/>
-      <c r="U82" s="83"/>
+      <c r="D82" s="71"/>
+      <c r="E82" s="72"/>
+      <c r="F82" s="72"/>
+      <c r="G82" s="72"/>
+      <c r="H82" s="72"/>
+      <c r="I82" s="72"/>
+      <c r="J82" s="72"/>
+      <c r="K82" s="72"/>
+      <c r="L82" s="72"/>
+      <c r="M82" s="72"/>
+      <c r="N82" s="72"/>
+      <c r="O82" s="72"/>
+      <c r="P82" s="72"/>
+      <c r="Q82" s="72"/>
+      <c r="R82" s="72"/>
+      <c r="S82" s="72"/>
+      <c r="T82" s="72"/>
+      <c r="U82" s="73"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="71"/>
+      <c r="A83" s="63"/>
       <c r="B83" s="35" t="s">
         <v>125</v>
       </c>
       <c r="C83" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="D83" s="90"/>
-      <c r="E83" s="82"/>
-      <c r="F83" s="82"/>
-      <c r="G83" s="82"/>
-      <c r="H83" s="82"/>
-      <c r="I83" s="82"/>
-      <c r="J83" s="82"/>
-      <c r="K83" s="82"/>
-      <c r="L83" s="82"/>
-      <c r="M83" s="82"/>
-      <c r="N83" s="82"/>
-      <c r="O83" s="82"/>
-      <c r="P83" s="82"/>
-      <c r="Q83" s="82"/>
-      <c r="R83" s="82"/>
-      <c r="S83" s="82"/>
-      <c r="T83" s="82"/>
-      <c r="U83" s="83"/>
+      <c r="D83" s="71"/>
+      <c r="E83" s="72"/>
+      <c r="F83" s="72"/>
+      <c r="G83" s="72"/>
+      <c r="H83" s="72"/>
+      <c r="I83" s="72"/>
+      <c r="J83" s="72"/>
+      <c r="K83" s="72"/>
+      <c r="L83" s="72"/>
+      <c r="M83" s="72"/>
+      <c r="N83" s="72"/>
+      <c r="O83" s="72"/>
+      <c r="P83" s="72"/>
+      <c r="Q83" s="72"/>
+      <c r="R83" s="72"/>
+      <c r="S83" s="72"/>
+      <c r="T83" s="72"/>
+      <c r="U83" s="73"/>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="71"/>
+      <c r="A84" s="63"/>
       <c r="B84" s="35" t="s">
         <v>126</v>
       </c>
       <c r="C84" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="D84" s="90"/>
-      <c r="E84" s="82"/>
-      <c r="F84" s="82"/>
-      <c r="G84" s="82"/>
-      <c r="H84" s="82"/>
-      <c r="I84" s="82"/>
-      <c r="J84" s="82"/>
-      <c r="K84" s="82"/>
-      <c r="L84" s="82"/>
-      <c r="M84" s="82"/>
-      <c r="N84" s="82"/>
-      <c r="O84" s="82"/>
-      <c r="P84" s="82"/>
-      <c r="Q84" s="82"/>
-      <c r="R84" s="82"/>
-      <c r="S84" s="82"/>
-      <c r="T84" s="82"/>
-      <c r="U84" s="83"/>
+      <c r="D84" s="71"/>
+      <c r="E84" s="72"/>
+      <c r="F84" s="72"/>
+      <c r="G84" s="72"/>
+      <c r="H84" s="72"/>
+      <c r="I84" s="72"/>
+      <c r="J84" s="72"/>
+      <c r="K84" s="72"/>
+      <c r="L84" s="72"/>
+      <c r="M84" s="72"/>
+      <c r="N84" s="72"/>
+      <c r="O84" s="72"/>
+      <c r="P84" s="72"/>
+      <c r="Q84" s="72"/>
+      <c r="R84" s="72"/>
+      <c r="S84" s="72"/>
+      <c r="T84" s="72"/>
+      <c r="U84" s="73"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="71"/>
+      <c r="A85" s="63"/>
       <c r="B85" s="35" t="s">
         <v>127</v>
       </c>
       <c r="C85" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="D85" s="90"/>
-      <c r="E85" s="82"/>
-      <c r="F85" s="82"/>
-      <c r="G85" s="82"/>
-      <c r="H85" s="82"/>
-      <c r="I85" s="82"/>
-      <c r="J85" s="82"/>
-      <c r="K85" s="82"/>
-      <c r="L85" s="82"/>
-      <c r="M85" s="82"/>
-      <c r="N85" s="82"/>
-      <c r="O85" s="82"/>
-      <c r="P85" s="82"/>
-      <c r="Q85" s="82"/>
-      <c r="R85" s="82"/>
-      <c r="S85" s="82"/>
-      <c r="T85" s="82"/>
-      <c r="U85" s="83"/>
+      <c r="D85" s="71"/>
+      <c r="E85" s="72"/>
+      <c r="F85" s="72"/>
+      <c r="G85" s="72"/>
+      <c r="H85" s="72"/>
+      <c r="I85" s="72"/>
+      <c r="J85" s="72"/>
+      <c r="K85" s="72"/>
+      <c r="L85" s="72"/>
+      <c r="M85" s="72"/>
+      <c r="N85" s="72"/>
+      <c r="O85" s="72"/>
+      <c r="P85" s="72"/>
+      <c r="Q85" s="72"/>
+      <c r="R85" s="72"/>
+      <c r="S85" s="72"/>
+      <c r="T85" s="72"/>
+      <c r="U85" s="73"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="71"/>
+      <c r="A86" s="63"/>
       <c r="B86" s="35" t="s">
         <v>128</v>
       </c>
       <c r="C86" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="D86" s="90"/>
-      <c r="E86" s="82"/>
-      <c r="F86" s="82"/>
-      <c r="G86" s="82"/>
-      <c r="H86" s="82"/>
-      <c r="I86" s="82"/>
-      <c r="J86" s="82"/>
-      <c r="K86" s="82"/>
-      <c r="L86" s="82"/>
-      <c r="M86" s="82"/>
-      <c r="N86" s="82"/>
-      <c r="O86" s="82"/>
-      <c r="P86" s="82"/>
-      <c r="Q86" s="82"/>
-      <c r="R86" s="82"/>
-      <c r="S86" s="82"/>
-      <c r="T86" s="82"/>
-      <c r="U86" s="83"/>
+      <c r="D86" s="71"/>
+      <c r="E86" s="72"/>
+      <c r="F86" s="72"/>
+      <c r="G86" s="72"/>
+      <c r="H86" s="72"/>
+      <c r="I86" s="72"/>
+      <c r="J86" s="72"/>
+      <c r="K86" s="72"/>
+      <c r="L86" s="72"/>
+      <c r="M86" s="72"/>
+      <c r="N86" s="72"/>
+      <c r="O86" s="72"/>
+      <c r="P86" s="72"/>
+      <c r="Q86" s="72"/>
+      <c r="R86" s="72"/>
+      <c r="S86" s="72"/>
+      <c r="T86" s="72"/>
+      <c r="U86" s="73"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="71"/>
+      <c r="A87" s="63"/>
       <c r="B87" s="35" t="s">
         <v>129</v>
       </c>
       <c r="C87" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="D87" s="90"/>
-      <c r="E87" s="82"/>
-      <c r="F87" s="82"/>
-      <c r="G87" s="82"/>
-      <c r="H87" s="82"/>
-      <c r="I87" s="82"/>
-      <c r="J87" s="82"/>
-      <c r="K87" s="82"/>
-      <c r="L87" s="82"/>
-      <c r="M87" s="82"/>
-      <c r="N87" s="82"/>
-      <c r="O87" s="82"/>
-      <c r="P87" s="82"/>
-      <c r="Q87" s="82"/>
-      <c r="R87" s="82"/>
-      <c r="S87" s="82"/>
-      <c r="T87" s="82"/>
-      <c r="U87" s="83"/>
+      <c r="D87" s="71"/>
+      <c r="E87" s="72"/>
+      <c r="F87" s="72"/>
+      <c r="G87" s="72"/>
+      <c r="H87" s="72"/>
+      <c r="I87" s="72"/>
+      <c r="J87" s="72"/>
+      <c r="K87" s="72"/>
+      <c r="L87" s="72"/>
+      <c r="M87" s="72"/>
+      <c r="N87" s="72"/>
+      <c r="O87" s="72"/>
+      <c r="P87" s="72"/>
+      <c r="Q87" s="72"/>
+      <c r="R87" s="72"/>
+      <c r="S87" s="72"/>
+      <c r="T87" s="72"/>
+      <c r="U87" s="73"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A88" s="64">
+      <c r="A88" s="67">
         <v>13</v>
       </c>
       <c r="B88" s="39" t="s">
@@ -10001,189 +10001,189 @@
       <c r="C88" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D88" s="90"/>
-      <c r="E88" s="82"/>
-      <c r="F88" s="82"/>
-      <c r="G88" s="82"/>
-      <c r="H88" s="82"/>
-      <c r="I88" s="82"/>
-      <c r="J88" s="82"/>
-      <c r="K88" s="82"/>
-      <c r="L88" s="82"/>
-      <c r="M88" s="82"/>
-      <c r="N88" s="82"/>
-      <c r="O88" s="82"/>
-      <c r="P88" s="82"/>
-      <c r="Q88" s="82"/>
-      <c r="R88" s="82"/>
-      <c r="S88" s="82"/>
-      <c r="T88" s="82"/>
-      <c r="U88" s="83"/>
+      <c r="D88" s="71"/>
+      <c r="E88" s="72"/>
+      <c r="F88" s="72"/>
+      <c r="G88" s="72"/>
+      <c r="H88" s="72"/>
+      <c r="I88" s="72"/>
+      <c r="J88" s="72"/>
+      <c r="K88" s="72"/>
+      <c r="L88" s="72"/>
+      <c r="M88" s="72"/>
+      <c r="N88" s="72"/>
+      <c r="O88" s="72"/>
+      <c r="P88" s="72"/>
+      <c r="Q88" s="72"/>
+      <c r="R88" s="72"/>
+      <c r="S88" s="72"/>
+      <c r="T88" s="72"/>
+      <c r="U88" s="73"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A89" s="64"/>
+      <c r="A89" s="67"/>
       <c r="B89" s="39" t="s">
         <v>131</v>
       </c>
       <c r="C89" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D89" s="90"/>
-      <c r="E89" s="82"/>
-      <c r="F89" s="82"/>
-      <c r="G89" s="82"/>
-      <c r="H89" s="82"/>
-      <c r="I89" s="82"/>
-      <c r="J89" s="82"/>
-      <c r="K89" s="82"/>
-      <c r="L89" s="82"/>
-      <c r="M89" s="82"/>
-      <c r="N89" s="82"/>
-      <c r="O89" s="82"/>
-      <c r="P89" s="82"/>
-      <c r="Q89" s="82"/>
-      <c r="R89" s="82"/>
-      <c r="S89" s="82"/>
-      <c r="T89" s="82"/>
-      <c r="U89" s="83"/>
+      <c r="D89" s="71"/>
+      <c r="E89" s="72"/>
+      <c r="F89" s="72"/>
+      <c r="G89" s="72"/>
+      <c r="H89" s="72"/>
+      <c r="I89" s="72"/>
+      <c r="J89" s="72"/>
+      <c r="K89" s="72"/>
+      <c r="L89" s="72"/>
+      <c r="M89" s="72"/>
+      <c r="N89" s="72"/>
+      <c r="O89" s="72"/>
+      <c r="P89" s="72"/>
+      <c r="Q89" s="72"/>
+      <c r="R89" s="72"/>
+      <c r="S89" s="72"/>
+      <c r="T89" s="72"/>
+      <c r="U89" s="73"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="64"/>
+      <c r="A90" s="67"/>
       <c r="B90" s="39" t="s">
         <v>132</v>
       </c>
       <c r="C90" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D90" s="90"/>
-      <c r="E90" s="82"/>
-      <c r="F90" s="82"/>
-      <c r="G90" s="82"/>
-      <c r="H90" s="82"/>
-      <c r="I90" s="82"/>
-      <c r="J90" s="82"/>
-      <c r="K90" s="82"/>
-      <c r="L90" s="82"/>
-      <c r="M90" s="82"/>
-      <c r="N90" s="82"/>
-      <c r="O90" s="82"/>
-      <c r="P90" s="82"/>
-      <c r="Q90" s="82"/>
-      <c r="R90" s="82"/>
-      <c r="S90" s="82"/>
-      <c r="T90" s="82"/>
-      <c r="U90" s="83"/>
+      <c r="D90" s="71"/>
+      <c r="E90" s="72"/>
+      <c r="F90" s="72"/>
+      <c r="G90" s="72"/>
+      <c r="H90" s="72"/>
+      <c r="I90" s="72"/>
+      <c r="J90" s="72"/>
+      <c r="K90" s="72"/>
+      <c r="L90" s="72"/>
+      <c r="M90" s="72"/>
+      <c r="N90" s="72"/>
+      <c r="O90" s="72"/>
+      <c r="P90" s="72"/>
+      <c r="Q90" s="72"/>
+      <c r="R90" s="72"/>
+      <c r="S90" s="72"/>
+      <c r="T90" s="72"/>
+      <c r="U90" s="73"/>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="64"/>
+      <c r="A91" s="67"/>
       <c r="B91" s="39" t="s">
         <v>133</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D91" s="90"/>
-      <c r="E91" s="82"/>
-      <c r="F91" s="82"/>
-      <c r="G91" s="82"/>
-      <c r="H91" s="82"/>
-      <c r="I91" s="82"/>
-      <c r="J91" s="82"/>
-      <c r="K91" s="82"/>
-      <c r="L91" s="82"/>
-      <c r="M91" s="82"/>
-      <c r="N91" s="82"/>
-      <c r="O91" s="82"/>
-      <c r="P91" s="82"/>
-      <c r="Q91" s="82"/>
-      <c r="R91" s="82"/>
-      <c r="S91" s="82"/>
-      <c r="T91" s="82"/>
-      <c r="U91" s="83"/>
+      <c r="D91" s="71"/>
+      <c r="E91" s="72"/>
+      <c r="F91" s="72"/>
+      <c r="G91" s="72"/>
+      <c r="H91" s="72"/>
+      <c r="I91" s="72"/>
+      <c r="J91" s="72"/>
+      <c r="K91" s="72"/>
+      <c r="L91" s="72"/>
+      <c r="M91" s="72"/>
+      <c r="N91" s="72"/>
+      <c r="O91" s="72"/>
+      <c r="P91" s="72"/>
+      <c r="Q91" s="72"/>
+      <c r="R91" s="72"/>
+      <c r="S91" s="72"/>
+      <c r="T91" s="72"/>
+      <c r="U91" s="73"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A92" s="64"/>
+      <c r="A92" s="67"/>
       <c r="B92" s="39" t="s">
         <v>134</v>
       </c>
       <c r="C92" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D92" s="90"/>
-      <c r="E92" s="82"/>
-      <c r="F92" s="82"/>
-      <c r="G92" s="82"/>
-      <c r="H92" s="82"/>
-      <c r="I92" s="82"/>
-      <c r="J92" s="82"/>
-      <c r="K92" s="82"/>
-      <c r="L92" s="82"/>
-      <c r="M92" s="82"/>
-      <c r="N92" s="82"/>
-      <c r="O92" s="82"/>
-      <c r="P92" s="82"/>
-      <c r="Q92" s="82"/>
-      <c r="R92" s="82"/>
-      <c r="S92" s="82"/>
-      <c r="T92" s="82"/>
-      <c r="U92" s="83"/>
+      <c r="D92" s="71"/>
+      <c r="E92" s="72"/>
+      <c r="F92" s="72"/>
+      <c r="G92" s="72"/>
+      <c r="H92" s="72"/>
+      <c r="I92" s="72"/>
+      <c r="J92" s="72"/>
+      <c r="K92" s="72"/>
+      <c r="L92" s="72"/>
+      <c r="M92" s="72"/>
+      <c r="N92" s="72"/>
+      <c r="O92" s="72"/>
+      <c r="P92" s="72"/>
+      <c r="Q92" s="72"/>
+      <c r="R92" s="72"/>
+      <c r="S92" s="72"/>
+      <c r="T92" s="72"/>
+      <c r="U92" s="73"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A93" s="64"/>
+      <c r="A93" s="67"/>
       <c r="B93" s="39" t="s">
         <v>135</v>
       </c>
       <c r="C93" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D93" s="90"/>
-      <c r="E93" s="82"/>
-      <c r="F93" s="82"/>
-      <c r="G93" s="82"/>
-      <c r="H93" s="82"/>
-      <c r="I93" s="82"/>
-      <c r="J93" s="82"/>
-      <c r="K93" s="82"/>
-      <c r="L93" s="82"/>
-      <c r="M93" s="82"/>
-      <c r="N93" s="82"/>
-      <c r="O93" s="82"/>
-      <c r="P93" s="82"/>
-      <c r="Q93" s="82"/>
-      <c r="R93" s="82"/>
-      <c r="S93" s="82"/>
-      <c r="T93" s="82"/>
-      <c r="U93" s="83"/>
+      <c r="D93" s="71"/>
+      <c r="E93" s="72"/>
+      <c r="F93" s="72"/>
+      <c r="G93" s="72"/>
+      <c r="H93" s="72"/>
+      <c r="I93" s="72"/>
+      <c r="J93" s="72"/>
+      <c r="K93" s="72"/>
+      <c r="L93" s="72"/>
+      <c r="M93" s="72"/>
+      <c r="N93" s="72"/>
+      <c r="O93" s="72"/>
+      <c r="P93" s="72"/>
+      <c r="Q93" s="72"/>
+      <c r="R93" s="72"/>
+      <c r="S93" s="72"/>
+      <c r="T93" s="72"/>
+      <c r="U93" s="73"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A94" s="64"/>
+      <c r="A94" s="67"/>
       <c r="B94" s="39" t="s">
         <v>136</v>
       </c>
       <c r="C94" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D94" s="91"/>
-      <c r="E94" s="84"/>
-      <c r="F94" s="84"/>
-      <c r="G94" s="84"/>
-      <c r="H94" s="84"/>
-      <c r="I94" s="84"/>
-      <c r="J94" s="84"/>
-      <c r="K94" s="84"/>
-      <c r="L94" s="84"/>
-      <c r="M94" s="84"/>
-      <c r="N94" s="84"/>
-      <c r="O94" s="84"/>
-      <c r="P94" s="84"/>
-      <c r="Q94" s="84"/>
-      <c r="R94" s="84"/>
-      <c r="S94" s="84"/>
-      <c r="T94" s="84"/>
-      <c r="U94" s="85"/>
+      <c r="D94" s="74"/>
+      <c r="E94" s="75"/>
+      <c r="F94" s="75"/>
+      <c r="G94" s="75"/>
+      <c r="H94" s="75"/>
+      <c r="I94" s="75"/>
+      <c r="J94" s="75"/>
+      <c r="K94" s="75"/>
+      <c r="L94" s="75"/>
+      <c r="M94" s="75"/>
+      <c r="N94" s="75"/>
+      <c r="O94" s="75"/>
+      <c r="P94" s="75"/>
+      <c r="Q94" s="75"/>
+      <c r="R94" s="75"/>
+      <c r="S94" s="75"/>
+      <c r="T94" s="75"/>
+      <c r="U94" s="76"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="71">
+      <c r="A95" s="63">
         <v>14</v>
       </c>
       <c r="B95" s="35" t="s">
@@ -10216,7 +10216,7 @@
       <c r="U95" s="15"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="71"/>
+      <c r="A96" s="63"/>
       <c r="B96" s="35" t="s">
         <v>139</v>
       </c>
@@ -10247,7 +10247,7 @@
       <c r="U96" s="15"/>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="71"/>
+      <c r="A97" s="63"/>
       <c r="B97" s="35" t="s">
         <v>140</v>
       </c>
@@ -10278,7 +10278,7 @@
       <c r="U97" s="15"/>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="71"/>
+      <c r="A98" s="63"/>
       <c r="B98" s="35" t="s">
         <v>141</v>
       </c>
@@ -10309,7 +10309,7 @@
       <c r="U98" s="15"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="71"/>
+      <c r="A99" s="63"/>
       <c r="B99" s="35" t="s">
         <v>142</v>
       </c>
@@ -10340,7 +10340,7 @@
       <c r="U99" s="15"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="71"/>
+      <c r="A100" s="63"/>
       <c r="B100" s="35" t="s">
         <v>143</v>
       </c>
@@ -10371,7 +10371,7 @@
       <c r="U100" s="15"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="71"/>
+      <c r="A101" s="63"/>
       <c r="B101" s="35" t="s">
         <v>144</v>
       </c>
@@ -10402,7 +10402,7 @@
       <c r="U101" s="15"/>
     </row>
     <row r="102" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="64">
+      <c r="A102" s="67">
         <v>15</v>
       </c>
       <c r="B102" s="39" t="s">
@@ -10435,7 +10435,7 @@
       <c r="U102" s="6"/>
     </row>
     <row r="103" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="64"/>
+      <c r="A103" s="67"/>
       <c r="B103" s="39" t="s">
         <v>146</v>
       </c>
@@ -10466,7 +10466,7 @@
       <c r="U103" s="6"/>
     </row>
     <row r="104" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="64"/>
+      <c r="A104" s="67"/>
       <c r="B104" s="39" t="s">
         <v>147</v>
       </c>
@@ -10497,7 +10497,7 @@
       <c r="U104" s="6"/>
     </row>
     <row r="105" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="64"/>
+      <c r="A105" s="67"/>
       <c r="B105" s="39" t="s">
         <v>148</v>
       </c>
@@ -10528,7 +10528,7 @@
       <c r="U105" s="6"/>
     </row>
     <row r="106" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="64"/>
+      <c r="A106" s="67"/>
       <c r="B106" s="39" t="s">
         <v>149</v>
       </c>
@@ -10559,7 +10559,7 @@
       <c r="U106" s="6"/>
     </row>
     <row r="107" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="64"/>
+      <c r="A107" s="67"/>
       <c r="B107" s="39" t="s">
         <v>150</v>
       </c>
@@ -10590,7 +10590,7 @@
       <c r="U107" s="6"/>
     </row>
     <row r="108" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="64"/>
+      <c r="A108" s="67"/>
       <c r="B108" s="39" t="s">
         <v>151</v>
       </c>
@@ -10621,7 +10621,7 @@
       <c r="U108" s="6"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="71">
+      <c r="A109" s="63">
         <v>16</v>
       </c>
       <c r="B109" s="35" t="s">
@@ -10654,7 +10654,7 @@
       <c r="U109" s="14"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="71"/>
+      <c r="A110" s="63"/>
       <c r="B110" s="35" t="s">
         <v>153</v>
       </c>
@@ -10685,7 +10685,7 @@
       <c r="U110" s="14"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="71"/>
+      <c r="A111" s="63"/>
       <c r="B111" s="35" t="s">
         <v>154</v>
       </c>
@@ -10716,7 +10716,7 @@
       <c r="U111" s="14"/>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="71"/>
+      <c r="A112" s="63"/>
       <c r="B112" s="35" t="s">
         <v>155</v>
       </c>
@@ -10747,7 +10747,7 @@
       <c r="U112" s="14"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="71"/>
+      <c r="A113" s="63"/>
       <c r="B113" s="35" t="s">
         <v>156</v>
       </c>
@@ -10778,7 +10778,7 @@
       <c r="U113" s="14"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="71"/>
+      <c r="A114" s="63"/>
       <c r="B114" s="35" t="s">
         <v>157</v>
       </c>
@@ -10809,7 +10809,7 @@
       <c r="U114" s="14"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="71"/>
+      <c r="A115" s="63"/>
       <c r="B115" s="35" t="s">
         <v>158</v>
       </c>
@@ -10840,7 +10840,7 @@
       <c r="U115" s="14"/>
     </row>
     <row r="116" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A116" s="64">
+      <c r="A116" s="67">
         <v>17</v>
       </c>
       <c r="B116" s="39" t="s">
@@ -10873,7 +10873,7 @@
       <c r="U116" s="6"/>
     </row>
     <row r="117" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A117" s="64"/>
+      <c r="A117" s="67"/>
       <c r="B117" s="39" t="s">
         <v>160</v>
       </c>
@@ -10904,7 +10904,7 @@
       <c r="U117" s="6"/>
     </row>
     <row r="118" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="64"/>
+      <c r="A118" s="67"/>
       <c r="B118" s="39" t="s">
         <v>161</v>
       </c>
@@ -10935,7 +10935,7 @@
       <c r="U118" s="6"/>
     </row>
     <row r="119" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="64"/>
+      <c r="A119" s="67"/>
       <c r="B119" s="39" t="s">
         <v>162</v>
       </c>
@@ -10966,7 +10966,7 @@
       <c r="U119" s="6"/>
     </row>
     <row r="120" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="64"/>
+      <c r="A120" s="67"/>
       <c r="B120" s="39" t="s">
         <v>163</v>
       </c>
@@ -10997,7 +10997,7 @@
       <c r="U120" s="6"/>
     </row>
     <row r="121" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="64"/>
+      <c r="A121" s="67"/>
       <c r="B121" s="39" t="s">
         <v>164</v>
       </c>
@@ -11028,7 +11028,7 @@
       <c r="U121" s="6"/>
     </row>
     <row r="122" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="64"/>
+      <c r="A122" s="67"/>
       <c r="B122" s="39" t="s">
         <v>165</v>
       </c>
@@ -11059,7 +11059,7 @@
       <c r="U122" s="6"/>
     </row>
     <row r="123" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="71">
+      <c r="A123" s="63">
         <v>18</v>
       </c>
       <c r="B123" s="35" t="s">
@@ -11092,7 +11092,7 @@
       <c r="U123" s="14"/>
     </row>
     <row r="124" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="71"/>
+      <c r="A124" s="63"/>
       <c r="B124" s="35" t="s">
         <v>167</v>
       </c>
@@ -11123,7 +11123,7 @@
       <c r="U124" s="14"/>
     </row>
     <row r="125" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="71"/>
+      <c r="A125" s="63"/>
       <c r="B125" s="35" t="s">
         <v>168</v>
       </c>
@@ -11154,7 +11154,7 @@
       <c r="U125" s="14"/>
     </row>
     <row r="126" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="71"/>
+      <c r="A126" s="63"/>
       <c r="B126" s="35" t="s">
         <v>169</v>
       </c>
@@ -11185,36 +11185,36 @@
       <c r="U126" s="14"/>
     </row>
     <row r="127" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="71"/>
+      <c r="A127" s="63"/>
       <c r="B127" s="34" t="s">
         <v>170</v>
       </c>
       <c r="C127" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="D127" s="77" t="s">
+      <c r="D127" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="E127" s="78"/>
-      <c r="F127" s="78"/>
-      <c r="G127" s="78"/>
-      <c r="H127" s="78"/>
-      <c r="I127" s="78"/>
-      <c r="J127" s="78"/>
-      <c r="K127" s="78"/>
-      <c r="L127" s="78"/>
-      <c r="M127" s="78"/>
-      <c r="N127" s="78"/>
-      <c r="O127" s="78"/>
-      <c r="P127" s="78"/>
-      <c r="Q127" s="78"/>
-      <c r="R127" s="78"/>
-      <c r="S127" s="78"/>
-      <c r="T127" s="78"/>
-      <c r="U127" s="79"/>
+      <c r="E127" s="65"/>
+      <c r="F127" s="65"/>
+      <c r="G127" s="65"/>
+      <c r="H127" s="65"/>
+      <c r="I127" s="65"/>
+      <c r="J127" s="65"/>
+      <c r="K127" s="65"/>
+      <c r="L127" s="65"/>
+      <c r="M127" s="65"/>
+      <c r="N127" s="65"/>
+      <c r="O127" s="65"/>
+      <c r="P127" s="65"/>
+      <c r="Q127" s="65"/>
+      <c r="R127" s="65"/>
+      <c r="S127" s="65"/>
+      <c r="T127" s="65"/>
+      <c r="U127" s="66"/>
     </row>
     <row r="128" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="71"/>
+      <c r="A128" s="63"/>
       <c r="B128" s="35" t="s">
         <v>171</v>
       </c>
@@ -11245,7 +11245,7 @@
       <c r="U128" s="14"/>
     </row>
     <row r="129" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="71"/>
+      <c r="A129" s="63"/>
       <c r="B129" s="35" t="s">
         <v>172</v>
       </c>
@@ -11276,7 +11276,7 @@
       <c r="U129" s="14"/>
     </row>
     <row r="130" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A130" s="64">
+      <c r="A130" s="67">
         <v>19</v>
       </c>
       <c r="B130" s="39" t="s">
@@ -11309,7 +11309,7 @@
       <c r="U130" s="6"/>
     </row>
     <row r="131" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A131" s="64"/>
+      <c r="A131" s="67"/>
       <c r="B131" s="39" t="s">
         <v>174</v>
       </c>
@@ -11340,7 +11340,7 @@
       <c r="U131" s="6"/>
     </row>
     <row r="132" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A132" s="64"/>
+      <c r="A132" s="67"/>
       <c r="B132" s="39" t="s">
         <v>175</v>
       </c>
@@ -11371,7 +11371,7 @@
       <c r="U132" s="6"/>
     </row>
     <row r="133" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A133" s="64"/>
+      <c r="A133" s="67"/>
       <c r="B133" s="39" t="s">
         <v>176</v>
       </c>
@@ -11402,7 +11402,7 @@
       <c r="U133" s="6"/>
     </row>
     <row r="134" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A134" s="64"/>
+      <c r="A134" s="67"/>
       <c r="B134" s="39" t="s">
         <v>177</v>
       </c>
@@ -11433,7 +11433,7 @@
       <c r="U134" s="6"/>
     </row>
     <row r="135" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A135" s="64"/>
+      <c r="A135" s="67"/>
       <c r="B135" s="39" t="s">
         <v>178</v>
       </c>
@@ -11464,7 +11464,7 @@
       <c r="U135" s="6"/>
     </row>
     <row r="136" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A136" s="64"/>
+      <c r="A136" s="67"/>
       <c r="B136" s="39" t="s">
         <v>179</v>
       </c>
@@ -11510,28 +11510,6 @@
     <row r="150" ht="20.25"/>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A123:A129"/>
-    <mergeCell ref="D127:U127"/>
-    <mergeCell ref="A130:A136"/>
-    <mergeCell ref="D81:U94"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A102:A108"/>
-    <mergeCell ref="A109:A115"/>
-    <mergeCell ref="A116:A122"/>
-    <mergeCell ref="A81:A87"/>
-    <mergeCell ref="A46:A52"/>
-    <mergeCell ref="A53:A59"/>
-    <mergeCell ref="A60:A66"/>
-    <mergeCell ref="A67:A73"/>
-    <mergeCell ref="A74:A80"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="D29:U31"/>
-    <mergeCell ref="M2:O2"/>
     <mergeCell ref="A32:A38"/>
     <mergeCell ref="D35:U41"/>
     <mergeCell ref="A39:A45"/>
@@ -11547,6 +11525,28 @@
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="D29:U31"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="A46:A52"/>
+    <mergeCell ref="A53:A59"/>
+    <mergeCell ref="A60:A66"/>
+    <mergeCell ref="A67:A73"/>
+    <mergeCell ref="A74:A80"/>
+    <mergeCell ref="A123:A129"/>
+    <mergeCell ref="D127:U127"/>
+    <mergeCell ref="A130:A136"/>
+    <mergeCell ref="D81:U94"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="A95:A101"/>
+    <mergeCell ref="A102:A108"/>
+    <mergeCell ref="A109:A115"/>
+    <mergeCell ref="A116:A122"/>
+    <mergeCell ref="A81:A87"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11589,81 +11589,81 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="73" t="s">
+      <c r="B2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="74"/>
-      <c r="D2" s="63" t="s">
+      <c r="C2" s="89"/>
+      <c r="D2" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63" t="s">
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="63" t="s">
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="63"/>
-      <c r="L2" s="63"/>
-      <c r="M2" s="63" t="s">
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="63"/>
-      <c r="O2" s="63"/>
-      <c r="P2" s="63" t="s">
+      <c r="N2" s="77"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="63"/>
-      <c r="R2" s="63"/>
-      <c r="S2" s="63" t="s">
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="63"/>
-      <c r="U2" s="63"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
     </row>
     <row r="3" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="72" t="s">
+      <c r="A3" s="77"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="87" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="63" t="s">
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63" t="s">
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="63"/>
-      <c r="L3" s="63"/>
-      <c r="M3" s="63" t="s">
+      <c r="K3" s="77"/>
+      <c r="L3" s="77"/>
+      <c r="M3" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="63"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63" t="s">
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="64">
+      <c r="A4" s="67">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -11721,7 +11721,7 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="64"/>
+      <c r="A5" s="67"/>
       <c r="B5" s="2" t="s">
         <v>23</v>
       </c>
@@ -11785,7 +11785,7 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="64"/>
+      <c r="A6" s="67"/>
       <c r="B6" s="2" t="s">
         <v>27</v>
       </c>
@@ -11849,7 +11849,7 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="64"/>
+      <c r="A7" s="67"/>
       <c r="B7" s="2" t="s">
         <v>29</v>
       </c>
@@ -11911,7 +11911,7 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="64"/>
+      <c r="A8" s="67"/>
       <c r="B8" s="2" t="s">
         <v>32</v>
       </c>
@@ -11957,7 +11957,7 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="64"/>
+      <c r="A9" s="67"/>
       <c r="B9" s="2" t="s">
         <v>37</v>
       </c>
@@ -11999,7 +11999,7 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="64"/>
+      <c r="A10" s="67"/>
       <c r="B10" s="2" t="s">
         <v>40</v>
       </c>
@@ -12043,7 +12043,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="71">
+      <c r="A11" s="63">
         <v>2</v>
       </c>
       <c r="B11" s="11" t="s">
@@ -12089,7 +12089,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="71"/>
+      <c r="A12" s="63"/>
       <c r="B12" s="11" t="s">
         <v>46</v>
       </c>
@@ -12151,7 +12151,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="71"/>
+      <c r="A13" s="63"/>
       <c r="B13" s="11" t="s">
         <v>48</v>
       </c>
@@ -12203,7 +12203,7 @@
       <c r="AA13" s="10"/>
     </row>
     <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="71"/>
+      <c r="A14" s="63"/>
       <c r="B14" s="11" t="s">
         <v>49</v>
       </c>
@@ -12249,7 +12249,7 @@
       <c r="AA14" s="10"/>
     </row>
     <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="71"/>
+      <c r="A15" s="63"/>
       <c r="B15" s="11" t="s">
         <v>53</v>
       </c>
@@ -12283,7 +12283,7 @@
       <c r="AA15" s="10"/>
     </row>
     <row r="16" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="71"/>
+      <c r="A16" s="63"/>
       <c r="B16" s="11" t="s">
         <v>54</v>
       </c>
@@ -12310,7 +12310,7 @@
       <c r="U16" s="15"/>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="71"/>
+      <c r="A17" s="63"/>
       <c r="B17" s="11" t="s">
         <v>55</v>
       </c>
@@ -12337,7 +12337,7 @@
       <c r="U17" s="15"/>
     </row>
     <row r="18" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="64">
+      <c r="A18" s="67">
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -12386,7 +12386,7 @@
       <c r="U18" s="6"/>
     </row>
     <row r="19" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="64"/>
+      <c r="A19" s="67"/>
       <c r="B19" s="2" t="s">
         <v>57</v>
       </c>
@@ -12433,7 +12433,7 @@
       <c r="U19" s="6"/>
     </row>
     <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="64"/>
+      <c r="A20" s="67"/>
       <c r="B20" s="2" t="s">
         <v>58</v>
       </c>
@@ -12480,7 +12480,7 @@
       <c r="U20" s="6"/>
     </row>
     <row r="21" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="64"/>
+      <c r="A21" s="67"/>
       <c r="B21" s="2" t="s">
         <v>60</v>
       </c>
@@ -12539,7 +12539,7 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="64"/>
+      <c r="A22" s="67"/>
       <c r="B22" s="2" t="s">
         <v>61</v>
       </c>
@@ -12586,7 +12586,7 @@
       <c r="U22" s="6"/>
     </row>
     <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="64"/>
+      <c r="A23" s="67"/>
       <c r="B23" s="2" t="s">
         <v>62</v>
       </c>
@@ -12613,7 +12613,7 @@
       <c r="U23" s="6"/>
     </row>
     <row r="24" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="64"/>
+      <c r="A24" s="67"/>
       <c r="B24" s="19" t="s">
         <v>63</v>
       </c>
@@ -12658,7 +12658,7 @@
       <c r="U24" s="26"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="71">
+      <c r="A25" s="63">
         <v>4</v>
       </c>
       <c r="B25" s="11" t="s">
@@ -12689,7 +12689,7 @@
       <c r="U25" s="15"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="71"/>
+      <c r="A26" s="63"/>
       <c r="B26" s="11" t="s">
         <v>65</v>
       </c>
@@ -12736,7 +12736,7 @@
       <c r="U26" s="15"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="71"/>
+      <c r="A27" s="63"/>
       <c r="B27" s="11" t="s">
         <v>66</v>
       </c>
@@ -12783,7 +12783,7 @@
       <c r="U27" s="15"/>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="71"/>
+      <c r="A28" s="63"/>
       <c r="B28" s="11" t="s">
         <v>67</v>
       </c>
@@ -12812,90 +12812,90 @@
       <c r="U28" s="15"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="71"/>
+      <c r="A29" s="63"/>
       <c r="B29" s="32" t="s">
         <v>68</v>
       </c>
       <c r="C29" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="D29" s="65" t="s">
+      <c r="D29" s="79" t="s">
         <v>69</v>
       </c>
-      <c r="E29" s="65"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
-      <c r="H29" s="65"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="65"/>
-      <c r="K29" s="65"/>
-      <c r="L29" s="65"/>
-      <c r="M29" s="65"/>
-      <c r="N29" s="65"/>
-      <c r="O29" s="65"/>
-      <c r="P29" s="65"/>
-      <c r="Q29" s="65"/>
-      <c r="R29" s="65"/>
-      <c r="S29" s="65"/>
-      <c r="T29" s="65"/>
-      <c r="U29" s="66"/>
+      <c r="E29" s="79"/>
+      <c r="F29" s="79"/>
+      <c r="G29" s="79"/>
+      <c r="H29" s="79"/>
+      <c r="I29" s="79"/>
+      <c r="J29" s="79"/>
+      <c r="K29" s="79"/>
+      <c r="L29" s="79"/>
+      <c r="M29" s="79"/>
+      <c r="N29" s="79"/>
+      <c r="O29" s="79"/>
+      <c r="P29" s="79"/>
+      <c r="Q29" s="79"/>
+      <c r="R29" s="79"/>
+      <c r="S29" s="79"/>
+      <c r="T29" s="79"/>
+      <c r="U29" s="80"/>
     </row>
     <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="71"/>
+      <c r="A30" s="63"/>
       <c r="B30" s="32" t="s">
         <v>70</v>
       </c>
       <c r="C30" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="D30" s="67"/>
-      <c r="E30" s="67"/>
-      <c r="F30" s="67"/>
-      <c r="G30" s="67"/>
-      <c r="H30" s="67"/>
-      <c r="I30" s="67"/>
-      <c r="J30" s="67"/>
-      <c r="K30" s="67"/>
-      <c r="L30" s="67"/>
-      <c r="M30" s="67"/>
-      <c r="N30" s="67"/>
-      <c r="O30" s="67"/>
-      <c r="P30" s="67"/>
-      <c r="Q30" s="67"/>
-      <c r="R30" s="67"/>
-      <c r="S30" s="67"/>
-      <c r="T30" s="67"/>
-      <c r="U30" s="68"/>
+      <c r="D30" s="82"/>
+      <c r="E30" s="82"/>
+      <c r="F30" s="82"/>
+      <c r="G30" s="82"/>
+      <c r="H30" s="82"/>
+      <c r="I30" s="82"/>
+      <c r="J30" s="82"/>
+      <c r="K30" s="82"/>
+      <c r="L30" s="82"/>
+      <c r="M30" s="82"/>
+      <c r="N30" s="82"/>
+      <c r="O30" s="82"/>
+      <c r="P30" s="82"/>
+      <c r="Q30" s="82"/>
+      <c r="R30" s="82"/>
+      <c r="S30" s="82"/>
+      <c r="T30" s="82"/>
+      <c r="U30" s="83"/>
     </row>
     <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="71"/>
+      <c r="A31" s="63"/>
       <c r="B31" s="32" t="s">
         <v>71</v>
       </c>
       <c r="C31" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="69"/>
-      <c r="E31" s="69"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="69"/>
-      <c r="H31" s="69"/>
-      <c r="I31" s="69"/>
-      <c r="J31" s="69"/>
-      <c r="K31" s="69"/>
-      <c r="L31" s="69"/>
-      <c r="M31" s="69"/>
-      <c r="N31" s="69"/>
-      <c r="O31" s="69"/>
-      <c r="P31" s="69"/>
-      <c r="Q31" s="69"/>
-      <c r="R31" s="69"/>
-      <c r="S31" s="69"/>
-      <c r="T31" s="69"/>
-      <c r="U31" s="70"/>
+      <c r="D31" s="85"/>
+      <c r="E31" s="85"/>
+      <c r="F31" s="85"/>
+      <c r="G31" s="85"/>
+      <c r="H31" s="85"/>
+      <c r="I31" s="85"/>
+      <c r="J31" s="85"/>
+      <c r="K31" s="85"/>
+      <c r="L31" s="85"/>
+      <c r="M31" s="85"/>
+      <c r="N31" s="85"/>
+      <c r="O31" s="85"/>
+      <c r="P31" s="85"/>
+      <c r="Q31" s="85"/>
+      <c r="R31" s="85"/>
+      <c r="S31" s="85"/>
+      <c r="T31" s="85"/>
+      <c r="U31" s="86"/>
     </row>
     <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="64">
+      <c r="A32" s="67">
         <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -12926,7 +12926,7 @@
       <c r="U32" s="6"/>
     </row>
     <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="64"/>
+      <c r="A33" s="67"/>
       <c r="B33" s="2" t="s">
         <v>73</v>
       </c>
@@ -12973,7 +12973,7 @@
       <c r="U33" s="6"/>
     </row>
     <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="64"/>
+      <c r="A34" s="67"/>
       <c r="B34" s="2" t="s">
         <v>74</v>
       </c>
@@ -13020,117 +13020,117 @@
       <c r="U34" s="6"/>
     </row>
     <row r="35" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="64"/>
+      <c r="A35" s="67"/>
       <c r="B35" s="47" t="s">
         <v>75</v>
       </c>
       <c r="C35" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="65" t="s">
+      <c r="D35" s="79" t="s">
         <v>69</v>
       </c>
-      <c r="E35" s="65"/>
-      <c r="F35" s="65"/>
-      <c r="G35" s="65"/>
-      <c r="H35" s="65"/>
-      <c r="I35" s="65"/>
-      <c r="J35" s="65"/>
-      <c r="K35" s="65"/>
-      <c r="L35" s="65"/>
-      <c r="M35" s="65"/>
-      <c r="N35" s="65"/>
-      <c r="O35" s="65"/>
-      <c r="P35" s="65"/>
-      <c r="Q35" s="65"/>
-      <c r="R35" s="65"/>
-      <c r="S35" s="65"/>
-      <c r="T35" s="65"/>
-      <c r="U35" s="66"/>
+      <c r="E35" s="79"/>
+      <c r="F35" s="79"/>
+      <c r="G35" s="79"/>
+      <c r="H35" s="79"/>
+      <c r="I35" s="79"/>
+      <c r="J35" s="79"/>
+      <c r="K35" s="79"/>
+      <c r="L35" s="79"/>
+      <c r="M35" s="79"/>
+      <c r="N35" s="79"/>
+      <c r="O35" s="79"/>
+      <c r="P35" s="79"/>
+      <c r="Q35" s="79"/>
+      <c r="R35" s="79"/>
+      <c r="S35" s="79"/>
+      <c r="T35" s="79"/>
+      <c r="U35" s="80"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="64"/>
+      <c r="A36" s="67"/>
       <c r="B36" s="47" t="s">
         <v>76</v>
       </c>
       <c r="C36" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="D36" s="67"/>
-      <c r="E36" s="67"/>
-      <c r="F36" s="67"/>
-      <c r="G36" s="67"/>
-      <c r="H36" s="67"/>
-      <c r="I36" s="67"/>
-      <c r="J36" s="67"/>
-      <c r="K36" s="67"/>
-      <c r="L36" s="67"/>
-      <c r="M36" s="67"/>
-      <c r="N36" s="67"/>
-      <c r="O36" s="67"/>
-      <c r="P36" s="67"/>
-      <c r="Q36" s="67"/>
-      <c r="R36" s="67"/>
-      <c r="S36" s="67"/>
-      <c r="T36" s="67"/>
-      <c r="U36" s="68"/>
+      <c r="D36" s="82"/>
+      <c r="E36" s="82"/>
+      <c r="F36" s="82"/>
+      <c r="G36" s="82"/>
+      <c r="H36" s="82"/>
+      <c r="I36" s="82"/>
+      <c r="J36" s="82"/>
+      <c r="K36" s="82"/>
+      <c r="L36" s="82"/>
+      <c r="M36" s="82"/>
+      <c r="N36" s="82"/>
+      <c r="O36" s="82"/>
+      <c r="P36" s="82"/>
+      <c r="Q36" s="82"/>
+      <c r="R36" s="82"/>
+      <c r="S36" s="82"/>
+      <c r="T36" s="82"/>
+      <c r="U36" s="83"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="64"/>
+      <c r="A37" s="67"/>
       <c r="B37" s="47" t="s">
         <v>77</v>
       </c>
       <c r="C37" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="D37" s="67"/>
-      <c r="E37" s="67"/>
-      <c r="F37" s="67"/>
-      <c r="G37" s="67"/>
-      <c r="H37" s="67"/>
-      <c r="I37" s="67"/>
-      <c r="J37" s="67"/>
-      <c r="K37" s="67"/>
-      <c r="L37" s="67"/>
-      <c r="M37" s="67"/>
-      <c r="N37" s="67"/>
-      <c r="O37" s="67"/>
-      <c r="P37" s="67"/>
-      <c r="Q37" s="67"/>
-      <c r="R37" s="67"/>
-      <c r="S37" s="67"/>
-      <c r="T37" s="67"/>
-      <c r="U37" s="68"/>
+      <c r="D37" s="82"/>
+      <c r="E37" s="82"/>
+      <c r="F37" s="82"/>
+      <c r="G37" s="82"/>
+      <c r="H37" s="82"/>
+      <c r="I37" s="82"/>
+      <c r="J37" s="82"/>
+      <c r="K37" s="82"/>
+      <c r="L37" s="82"/>
+      <c r="M37" s="82"/>
+      <c r="N37" s="82"/>
+      <c r="O37" s="82"/>
+      <c r="P37" s="82"/>
+      <c r="Q37" s="82"/>
+      <c r="R37" s="82"/>
+      <c r="S37" s="82"/>
+      <c r="T37" s="82"/>
+      <c r="U37" s="83"/>
     </row>
     <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="64"/>
+      <c r="A38" s="67"/>
       <c r="B38" s="47" t="s">
         <v>78</v>
       </c>
       <c r="C38" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="D38" s="67"/>
-      <c r="E38" s="67"/>
-      <c r="F38" s="67"/>
-      <c r="G38" s="67"/>
-      <c r="H38" s="67"/>
-      <c r="I38" s="67"/>
-      <c r="J38" s="67"/>
-      <c r="K38" s="67"/>
-      <c r="L38" s="67"/>
-      <c r="M38" s="67"/>
-      <c r="N38" s="67"/>
-      <c r="O38" s="67"/>
-      <c r="P38" s="67"/>
-      <c r="Q38" s="67"/>
-      <c r="R38" s="67"/>
-      <c r="S38" s="67"/>
-      <c r="T38" s="67"/>
-      <c r="U38" s="68"/>
+      <c r="D38" s="82"/>
+      <c r="E38" s="82"/>
+      <c r="F38" s="82"/>
+      <c r="G38" s="82"/>
+      <c r="H38" s="82"/>
+      <c r="I38" s="82"/>
+      <c r="J38" s="82"/>
+      <c r="K38" s="82"/>
+      <c r="L38" s="82"/>
+      <c r="M38" s="82"/>
+      <c r="N38" s="82"/>
+      <c r="O38" s="82"/>
+      <c r="P38" s="82"/>
+      <c r="Q38" s="82"/>
+      <c r="R38" s="82"/>
+      <c r="S38" s="82"/>
+      <c r="T38" s="82"/>
+      <c r="U38" s="83"/>
     </row>
     <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="71">
+      <c r="A39" s="63">
         <v>6</v>
       </c>
       <c r="B39" s="47" t="s">
@@ -13139,81 +13139,81 @@
       <c r="C39" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="67"/>
-      <c r="E39" s="67"/>
-      <c r="F39" s="67"/>
-      <c r="G39" s="67"/>
-      <c r="H39" s="67"/>
-      <c r="I39" s="67"/>
-      <c r="J39" s="67"/>
-      <c r="K39" s="67"/>
-      <c r="L39" s="67"/>
-      <c r="M39" s="67"/>
-      <c r="N39" s="67"/>
-      <c r="O39" s="67"/>
-      <c r="P39" s="67"/>
-      <c r="Q39" s="67"/>
-      <c r="R39" s="67"/>
-      <c r="S39" s="67"/>
-      <c r="T39" s="67"/>
-      <c r="U39" s="68"/>
+      <c r="D39" s="82"/>
+      <c r="E39" s="82"/>
+      <c r="F39" s="82"/>
+      <c r="G39" s="82"/>
+      <c r="H39" s="82"/>
+      <c r="I39" s="82"/>
+      <c r="J39" s="82"/>
+      <c r="K39" s="82"/>
+      <c r="L39" s="82"/>
+      <c r="M39" s="82"/>
+      <c r="N39" s="82"/>
+      <c r="O39" s="82"/>
+      <c r="P39" s="82"/>
+      <c r="Q39" s="82"/>
+      <c r="R39" s="82"/>
+      <c r="S39" s="82"/>
+      <c r="T39" s="82"/>
+      <c r="U39" s="83"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="71"/>
+      <c r="A40" s="63"/>
       <c r="B40" s="47" t="s">
         <v>80</v>
       </c>
       <c r="C40" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="D40" s="67"/>
-      <c r="E40" s="67"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="67"/>
-      <c r="H40" s="67"/>
-      <c r="I40" s="67"/>
-      <c r="J40" s="67"/>
-      <c r="K40" s="67"/>
-      <c r="L40" s="67"/>
-      <c r="M40" s="67"/>
-      <c r="N40" s="67"/>
-      <c r="O40" s="67"/>
-      <c r="P40" s="67"/>
-      <c r="Q40" s="67"/>
-      <c r="R40" s="67"/>
-      <c r="S40" s="67"/>
-      <c r="T40" s="67"/>
-      <c r="U40" s="68"/>
+      <c r="D40" s="82"/>
+      <c r="E40" s="82"/>
+      <c r="F40" s="82"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="82"/>
+      <c r="I40" s="82"/>
+      <c r="J40" s="82"/>
+      <c r="K40" s="82"/>
+      <c r="L40" s="82"/>
+      <c r="M40" s="82"/>
+      <c r="N40" s="82"/>
+      <c r="O40" s="82"/>
+      <c r="P40" s="82"/>
+      <c r="Q40" s="82"/>
+      <c r="R40" s="82"/>
+      <c r="S40" s="82"/>
+      <c r="T40" s="82"/>
+      <c r="U40" s="83"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="71"/>
+      <c r="A41" s="63"/>
       <c r="B41" s="47" t="s">
         <v>81</v>
       </c>
       <c r="C41" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="D41" s="69"/>
-      <c r="E41" s="69"/>
-      <c r="F41" s="69"/>
-      <c r="G41" s="69"/>
-      <c r="H41" s="69"/>
-      <c r="I41" s="69"/>
-      <c r="J41" s="69"/>
-      <c r="K41" s="69"/>
-      <c r="L41" s="69"/>
-      <c r="M41" s="69"/>
-      <c r="N41" s="69"/>
-      <c r="O41" s="69"/>
-      <c r="P41" s="69"/>
-      <c r="Q41" s="69"/>
-      <c r="R41" s="69"/>
-      <c r="S41" s="69"/>
-      <c r="T41" s="69"/>
-      <c r="U41" s="70"/>
+      <c r="D41" s="85"/>
+      <c r="E41" s="85"/>
+      <c r="F41" s="85"/>
+      <c r="G41" s="85"/>
+      <c r="H41" s="85"/>
+      <c r="I41" s="85"/>
+      <c r="J41" s="85"/>
+      <c r="K41" s="85"/>
+      <c r="L41" s="85"/>
+      <c r="M41" s="85"/>
+      <c r="N41" s="85"/>
+      <c r="O41" s="85"/>
+      <c r="P41" s="85"/>
+      <c r="Q41" s="85"/>
+      <c r="R41" s="85"/>
+      <c r="S41" s="85"/>
+      <c r="T41" s="85"/>
+      <c r="U41" s="86"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="71"/>
+      <c r="A42" s="63"/>
       <c r="B42" s="35" t="s">
         <v>82</v>
       </c>
@@ -13254,7 +13254,7 @@
       </c>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="71"/>
+      <c r="A43" s="63"/>
       <c r="B43" s="35" t="s">
         <v>83</v>
       </c>
@@ -13301,7 +13301,7 @@
       <c r="U43" s="15"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="71"/>
+      <c r="A44" s="63"/>
       <c r="B44" s="37" t="s">
         <v>84</v>
       </c>
@@ -13346,7 +13346,7 @@
       <c r="U44" s="26"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="71"/>
+      <c r="A45" s="63"/>
       <c r="B45" s="35" t="s">
         <v>86</v>
       </c>
@@ -13373,7 +13373,7 @@
       <c r="U45" s="15"/>
     </row>
     <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="64">
+      <c r="A46" s="67">
         <v>7</v>
       </c>
       <c r="B46" s="39" t="s">
@@ -13422,7 +13422,7 @@
       <c r="U46" s="6"/>
     </row>
     <row r="47" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="64"/>
+      <c r="A47" s="67"/>
       <c r="B47" s="39" t="s">
         <v>88</v>
       </c>
@@ -13469,7 +13469,7 @@
       <c r="U47" s="6"/>
     </row>
     <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="64"/>
+      <c r="A48" s="67"/>
       <c r="B48" s="39" t="s">
         <v>89</v>
       </c>
@@ -13516,7 +13516,7 @@
       <c r="U48" s="6"/>
     </row>
     <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="64"/>
+      <c r="A49" s="67"/>
       <c r="B49" s="39" t="s">
         <v>90</v>
       </c>
@@ -13563,7 +13563,7 @@
       <c r="U49" s="6"/>
     </row>
     <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="64"/>
+      <c r="A50" s="67"/>
       <c r="B50" s="39" t="s">
         <v>91</v>
       </c>
@@ -13610,7 +13610,7 @@
       <c r="U50" s="6"/>
     </row>
     <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="64"/>
+      <c r="A51" s="67"/>
       <c r="B51" s="39" t="s">
         <v>92</v>
       </c>
@@ -13637,7 +13637,7 @@
       <c r="U51" s="6"/>
     </row>
     <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="64"/>
+      <c r="A52" s="67"/>
       <c r="B52" s="39" t="s">
         <v>93</v>
       </c>
@@ -13664,7 +13664,7 @@
       <c r="U52" s="6"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="71">
+      <c r="A53" s="63">
         <v>8</v>
       </c>
       <c r="B53" s="35" t="s">
@@ -13695,7 +13695,7 @@
       <c r="U53" s="15"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="71"/>
+      <c r="A54" s="63"/>
       <c r="B54" s="35" t="s">
         <v>95</v>
       </c>
@@ -13742,7 +13742,7 @@
       <c r="U54" s="15"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="71"/>
+      <c r="A55" s="63"/>
       <c r="B55" s="35" t="s">
         <v>96</v>
       </c>
@@ -13789,7 +13789,7 @@
       <c r="U55" s="15"/>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="71"/>
+      <c r="A56" s="63"/>
       <c r="B56" s="35" t="s">
         <v>97</v>
       </c>
@@ -13830,7 +13830,7 @@
       </c>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="71"/>
+      <c r="A57" s="63"/>
       <c r="B57" s="35" t="s">
         <v>98</v>
       </c>
@@ -13877,7 +13877,7 @@
       <c r="U57" s="15"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="71"/>
+      <c r="A58" s="63"/>
       <c r="B58" s="35" t="s">
         <v>99</v>
       </c>
@@ -13887,33 +13887,15 @@
       <c r="D58" s="11"/>
       <c r="E58" s="13"/>
       <c r="F58" s="14"/>
-      <c r="G58" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="H58" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="I58" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="J58" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K58" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="L58" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="M58" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="N58" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="O58" s="15" t="s">
-        <v>85</v>
-      </c>
+      <c r="G58" s="11"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="15"/>
+      <c r="J58" s="11"/>
+      <c r="K58" s="13"/>
+      <c r="L58" s="15"/>
+      <c r="M58" s="11"/>
+      <c r="N58" s="13"/>
+      <c r="O58" s="15"/>
       <c r="P58" s="11"/>
       <c r="Q58" s="13"/>
       <c r="R58" s="15"/>
@@ -13922,7 +13904,7 @@
       <c r="U58" s="15"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="71"/>
+      <c r="A59" s="63"/>
       <c r="B59" s="35" t="s">
         <v>100</v>
       </c>
@@ -13949,7 +13931,7 @@
       <c r="U59" s="15"/>
     </row>
     <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="64">
+      <c r="A60" s="67">
         <v>9</v>
       </c>
       <c r="B60" s="39" t="s">
@@ -13980,7 +13962,7 @@
       <c r="U60" s="6"/>
     </row>
     <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="64"/>
+      <c r="A61" s="67"/>
       <c r="B61" s="39" t="s">
         <v>102</v>
       </c>
@@ -14027,7 +14009,7 @@
       <c r="U61" s="6"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="64"/>
+      <c r="A62" s="67"/>
       <c r="B62" s="39" t="s">
         <v>103</v>
       </c>
@@ -14074,7 +14056,7 @@
       <c r="U62" s="6"/>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="64"/>
+      <c r="A63" s="67"/>
       <c r="B63" s="39" t="s">
         <v>104</v>
       </c>
@@ -14115,7 +14097,7 @@
       </c>
     </row>
     <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="64"/>
+      <c r="A64" s="67"/>
       <c r="B64" s="39" t="s">
         <v>105</v>
       </c>
@@ -14162,7 +14144,7 @@
       <c r="U64" s="5"/>
     </row>
     <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="64"/>
+      <c r="A65" s="67"/>
       <c r="B65" s="39" t="s">
         <v>106</v>
       </c>
@@ -14189,7 +14171,7 @@
       <c r="U65" s="5"/>
     </row>
     <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="64"/>
+      <c r="A66" s="67"/>
       <c r="B66" s="39" t="s">
         <v>107</v>
       </c>
@@ -14216,7 +14198,7 @@
       <c r="U66" s="5"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="71">
+      <c r="A67" s="63">
         <v>10</v>
       </c>
       <c r="B67" s="35" t="s">
@@ -14265,7 +14247,7 @@
       <c r="U67" s="14"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="71"/>
+      <c r="A68" s="63"/>
       <c r="B68" s="35" t="s">
         <v>109</v>
       </c>
@@ -14312,7 +14294,7 @@
       <c r="U68" s="14"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="71"/>
+      <c r="A69" s="63"/>
       <c r="B69" s="35" t="s">
         <v>110</v>
       </c>
@@ -14359,7 +14341,7 @@
       <c r="U69" s="14"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="71"/>
+      <c r="A70" s="63"/>
       <c r="B70" s="35" t="s">
         <v>111</v>
       </c>
@@ -14418,7 +14400,7 @@
       </c>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="71"/>
+      <c r="A71" s="63"/>
       <c r="B71" s="35" t="s">
         <v>112</v>
       </c>
@@ -14465,7 +14447,7 @@
       <c r="U71" s="14"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="71"/>
+      <c r="A72" s="63"/>
       <c r="B72" s="35" t="s">
         <v>113</v>
       </c>
@@ -14475,15 +14457,33 @@
       <c r="D72" s="11"/>
       <c r="E72" s="13"/>
       <c r="F72" s="14"/>
-      <c r="G72" s="11"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="15"/>
-      <c r="J72" s="11"/>
-      <c r="K72" s="13"/>
-      <c r="L72" s="15"/>
-      <c r="M72" s="11"/>
-      <c r="N72" s="13"/>
-      <c r="O72" s="15"/>
+      <c r="G72" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H72" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="I72" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="J72" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="K72" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="L72" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="M72" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N72" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="O72" s="15" t="s">
+        <v>85</v>
+      </c>
       <c r="P72" s="11"/>
       <c r="Q72" s="13"/>
       <c r="R72" s="14"/>
@@ -14492,7 +14492,7 @@
       <c r="U72" s="14"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="71"/>
+      <c r="A73" s="63"/>
       <c r="B73" s="35" t="s">
         <v>114</v>
       </c>
@@ -14519,7 +14519,7 @@
       <c r="U73" s="14"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="64">
+      <c r="A74" s="67">
         <v>11</v>
       </c>
       <c r="B74" s="39" t="s">
@@ -14568,7 +14568,7 @@
       <c r="U74" s="62"/>
     </row>
     <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A75" s="64"/>
+      <c r="A75" s="67"/>
       <c r="B75" s="39" t="s">
         <v>116</v>
       </c>
@@ -14615,7 +14615,7 @@
       <c r="U75" s="62"/>
     </row>
     <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A76" s="64"/>
+      <c r="A76" s="67"/>
       <c r="B76" s="39" t="s">
         <v>117</v>
       </c>
@@ -14662,7 +14662,7 @@
       <c r="U76" s="62"/>
     </row>
     <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A77" s="64"/>
+      <c r="A77" s="67"/>
       <c r="B77" s="39" t="s">
         <v>118</v>
       </c>
@@ -14709,7 +14709,7 @@
       <c r="U77" s="62"/>
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A78" s="64"/>
+      <c r="A78" s="67"/>
       <c r="B78" s="3" t="s">
         <v>119</v>
       </c>
@@ -14756,7 +14756,7 @@
       <c r="U78" s="62"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A79" s="64"/>
+      <c r="A79" s="67"/>
       <c r="B79" s="3" t="s">
         <v>120</v>
       </c>
@@ -14783,7 +14783,7 @@
       <c r="U79" s="62"/>
     </row>
     <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A80" s="64"/>
+      <c r="A80" s="67"/>
       <c r="B80" s="3" t="s">
         <v>121</v>
       </c>
@@ -14810,7 +14810,7 @@
       <c r="U80" s="62"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="71">
+      <c r="A81" s="63">
         <v>12</v>
       </c>
       <c r="B81" s="12" t="s">
@@ -14819,191 +14819,191 @@
       <c r="C81" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="D81" s="80" t="s">
+      <c r="D81" s="69" t="s">
         <v>123</v>
       </c>
-      <c r="E81" s="80"/>
-      <c r="F81" s="80"/>
-      <c r="G81" s="80"/>
-      <c r="H81" s="80"/>
-      <c r="I81" s="80"/>
-      <c r="J81" s="80"/>
-      <c r="K81" s="80"/>
-      <c r="L81" s="80"/>
-      <c r="M81" s="80"/>
-      <c r="N81" s="80"/>
-      <c r="O81" s="80"/>
-      <c r="P81" s="80"/>
-      <c r="Q81" s="80"/>
-      <c r="R81" s="80"/>
-      <c r="S81" s="80"/>
-      <c r="T81" s="80"/>
-      <c r="U81" s="81"/>
+      <c r="E81" s="69"/>
+      <c r="F81" s="69"/>
+      <c r="G81" s="69"/>
+      <c r="H81" s="69"/>
+      <c r="I81" s="69"/>
+      <c r="J81" s="69"/>
+      <c r="K81" s="69"/>
+      <c r="L81" s="69"/>
+      <c r="M81" s="69"/>
+      <c r="N81" s="69"/>
+      <c r="O81" s="69"/>
+      <c r="P81" s="69"/>
+      <c r="Q81" s="69"/>
+      <c r="R81" s="69"/>
+      <c r="S81" s="69"/>
+      <c r="T81" s="69"/>
+      <c r="U81" s="70"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="71"/>
+      <c r="A82" s="63"/>
       <c r="B82" s="12" t="s">
         <v>124</v>
       </c>
       <c r="C82" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="D82" s="82"/>
-      <c r="E82" s="82"/>
-      <c r="F82" s="82"/>
-      <c r="G82" s="82"/>
-      <c r="H82" s="82"/>
-      <c r="I82" s="82"/>
-      <c r="J82" s="82"/>
-      <c r="K82" s="82"/>
-      <c r="L82" s="82"/>
-      <c r="M82" s="82"/>
-      <c r="N82" s="82"/>
-      <c r="O82" s="82"/>
-      <c r="P82" s="82"/>
-      <c r="Q82" s="82"/>
-      <c r="R82" s="82"/>
-      <c r="S82" s="82"/>
-      <c r="T82" s="82"/>
-      <c r="U82" s="83"/>
+      <c r="D82" s="72"/>
+      <c r="E82" s="72"/>
+      <c r="F82" s="72"/>
+      <c r="G82" s="72"/>
+      <c r="H82" s="72"/>
+      <c r="I82" s="72"/>
+      <c r="J82" s="72"/>
+      <c r="K82" s="72"/>
+      <c r="L82" s="72"/>
+      <c r="M82" s="72"/>
+      <c r="N82" s="72"/>
+      <c r="O82" s="72"/>
+      <c r="P82" s="72"/>
+      <c r="Q82" s="72"/>
+      <c r="R82" s="72"/>
+      <c r="S82" s="72"/>
+      <c r="T82" s="72"/>
+      <c r="U82" s="73"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="71"/>
+      <c r="A83" s="63"/>
       <c r="B83" s="12" t="s">
         <v>125</v>
       </c>
       <c r="C83" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="D83" s="82"/>
-      <c r="E83" s="82"/>
-      <c r="F83" s="82"/>
-      <c r="G83" s="82"/>
-      <c r="H83" s="82"/>
-      <c r="I83" s="82"/>
-      <c r="J83" s="82"/>
-      <c r="K83" s="82"/>
-      <c r="L83" s="82"/>
-      <c r="M83" s="82"/>
-      <c r="N83" s="82"/>
-      <c r="O83" s="82"/>
-      <c r="P83" s="82"/>
-      <c r="Q83" s="82"/>
-      <c r="R83" s="82"/>
-      <c r="S83" s="82"/>
-      <c r="T83" s="82"/>
-      <c r="U83" s="83"/>
+      <c r="D83" s="72"/>
+      <c r="E83" s="72"/>
+      <c r="F83" s="72"/>
+      <c r="G83" s="72"/>
+      <c r="H83" s="72"/>
+      <c r="I83" s="72"/>
+      <c r="J83" s="72"/>
+      <c r="K83" s="72"/>
+      <c r="L83" s="72"/>
+      <c r="M83" s="72"/>
+      <c r="N83" s="72"/>
+      <c r="O83" s="72"/>
+      <c r="P83" s="72"/>
+      <c r="Q83" s="72"/>
+      <c r="R83" s="72"/>
+      <c r="S83" s="72"/>
+      <c r="T83" s="72"/>
+      <c r="U83" s="73"/>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="71"/>
+      <c r="A84" s="63"/>
       <c r="B84" s="12" t="s">
         <v>126</v>
       </c>
       <c r="C84" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="D84" s="82"/>
-      <c r="E84" s="82"/>
-      <c r="F84" s="82"/>
-      <c r="G84" s="82"/>
-      <c r="H84" s="82"/>
-      <c r="I84" s="82"/>
-      <c r="J84" s="82"/>
-      <c r="K84" s="82"/>
-      <c r="L84" s="82"/>
-      <c r="M84" s="82"/>
-      <c r="N84" s="82"/>
-      <c r="O84" s="82"/>
-      <c r="P84" s="82"/>
-      <c r="Q84" s="82"/>
-      <c r="R84" s="82"/>
-      <c r="S84" s="82"/>
-      <c r="T84" s="82"/>
-      <c r="U84" s="83"/>
+      <c r="D84" s="72"/>
+      <c r="E84" s="72"/>
+      <c r="F84" s="72"/>
+      <c r="G84" s="72"/>
+      <c r="H84" s="72"/>
+      <c r="I84" s="72"/>
+      <c r="J84" s="72"/>
+      <c r="K84" s="72"/>
+      <c r="L84" s="72"/>
+      <c r="M84" s="72"/>
+      <c r="N84" s="72"/>
+      <c r="O84" s="72"/>
+      <c r="P84" s="72"/>
+      <c r="Q84" s="72"/>
+      <c r="R84" s="72"/>
+      <c r="S84" s="72"/>
+      <c r="T84" s="72"/>
+      <c r="U84" s="73"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="71"/>
+      <c r="A85" s="63"/>
       <c r="B85" s="12" t="s">
         <v>127</v>
       </c>
       <c r="C85" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="D85" s="82"/>
-      <c r="E85" s="82"/>
-      <c r="F85" s="82"/>
-      <c r="G85" s="82"/>
-      <c r="H85" s="82"/>
-      <c r="I85" s="82"/>
-      <c r="J85" s="82"/>
-      <c r="K85" s="82"/>
-      <c r="L85" s="82"/>
-      <c r="M85" s="82"/>
-      <c r="N85" s="82"/>
-      <c r="O85" s="82"/>
-      <c r="P85" s="82"/>
-      <c r="Q85" s="82"/>
-      <c r="R85" s="82"/>
-      <c r="S85" s="82"/>
-      <c r="T85" s="82"/>
-      <c r="U85" s="83"/>
+      <c r="D85" s="72"/>
+      <c r="E85" s="72"/>
+      <c r="F85" s="72"/>
+      <c r="G85" s="72"/>
+      <c r="H85" s="72"/>
+      <c r="I85" s="72"/>
+      <c r="J85" s="72"/>
+      <c r="K85" s="72"/>
+      <c r="L85" s="72"/>
+      <c r="M85" s="72"/>
+      <c r="N85" s="72"/>
+      <c r="O85" s="72"/>
+      <c r="P85" s="72"/>
+      <c r="Q85" s="72"/>
+      <c r="R85" s="72"/>
+      <c r="S85" s="72"/>
+      <c r="T85" s="72"/>
+      <c r="U85" s="73"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="71"/>
+      <c r="A86" s="63"/>
       <c r="B86" s="12" t="s">
         <v>128</v>
       </c>
       <c r="C86" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="D86" s="82"/>
-      <c r="E86" s="82"/>
-      <c r="F86" s="82"/>
-      <c r="G86" s="82"/>
-      <c r="H86" s="82"/>
-      <c r="I86" s="82"/>
-      <c r="J86" s="82"/>
-      <c r="K86" s="82"/>
-      <c r="L86" s="82"/>
-      <c r="M86" s="82"/>
-      <c r="N86" s="82"/>
-      <c r="O86" s="82"/>
-      <c r="P86" s="82"/>
-      <c r="Q86" s="82"/>
-      <c r="R86" s="82"/>
-      <c r="S86" s="82"/>
-      <c r="T86" s="82"/>
-      <c r="U86" s="83"/>
+      <c r="D86" s="72"/>
+      <c r="E86" s="72"/>
+      <c r="F86" s="72"/>
+      <c r="G86" s="72"/>
+      <c r="H86" s="72"/>
+      <c r="I86" s="72"/>
+      <c r="J86" s="72"/>
+      <c r="K86" s="72"/>
+      <c r="L86" s="72"/>
+      <c r="M86" s="72"/>
+      <c r="N86" s="72"/>
+      <c r="O86" s="72"/>
+      <c r="P86" s="72"/>
+      <c r="Q86" s="72"/>
+      <c r="R86" s="72"/>
+      <c r="S86" s="72"/>
+      <c r="T86" s="72"/>
+      <c r="U86" s="73"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="71"/>
+      <c r="A87" s="63"/>
       <c r="B87" s="12" t="s">
         <v>129</v>
       </c>
       <c r="C87" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="D87" s="82"/>
-      <c r="E87" s="82"/>
-      <c r="F87" s="82"/>
-      <c r="G87" s="82"/>
-      <c r="H87" s="82"/>
-      <c r="I87" s="82"/>
-      <c r="J87" s="82"/>
-      <c r="K87" s="82"/>
-      <c r="L87" s="82"/>
-      <c r="M87" s="82"/>
-      <c r="N87" s="82"/>
-      <c r="O87" s="82"/>
-      <c r="P87" s="82"/>
-      <c r="Q87" s="82"/>
-      <c r="R87" s="82"/>
-      <c r="S87" s="82"/>
-      <c r="T87" s="82"/>
-      <c r="U87" s="83"/>
+      <c r="D87" s="72"/>
+      <c r="E87" s="72"/>
+      <c r="F87" s="72"/>
+      <c r="G87" s="72"/>
+      <c r="H87" s="72"/>
+      <c r="I87" s="72"/>
+      <c r="J87" s="72"/>
+      <c r="K87" s="72"/>
+      <c r="L87" s="72"/>
+      <c r="M87" s="72"/>
+      <c r="N87" s="72"/>
+      <c r="O87" s="72"/>
+      <c r="P87" s="72"/>
+      <c r="Q87" s="72"/>
+      <c r="R87" s="72"/>
+      <c r="S87" s="72"/>
+      <c r="T87" s="72"/>
+      <c r="U87" s="73"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A88" s="64">
+      <c r="A88" s="67">
         <v>13</v>
       </c>
       <c r="B88" s="3" t="s">
@@ -15012,189 +15012,189 @@
       <c r="C88" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D88" s="82"/>
-      <c r="E88" s="82"/>
-      <c r="F88" s="82"/>
-      <c r="G88" s="82"/>
-      <c r="H88" s="82"/>
-      <c r="I88" s="82"/>
-      <c r="J88" s="82"/>
-      <c r="K88" s="82"/>
-      <c r="L88" s="82"/>
-      <c r="M88" s="82"/>
-      <c r="N88" s="82"/>
-      <c r="O88" s="82"/>
-      <c r="P88" s="82"/>
-      <c r="Q88" s="82"/>
-      <c r="R88" s="82"/>
-      <c r="S88" s="82"/>
-      <c r="T88" s="82"/>
-      <c r="U88" s="83"/>
+      <c r="D88" s="72"/>
+      <c r="E88" s="72"/>
+      <c r="F88" s="72"/>
+      <c r="G88" s="72"/>
+      <c r="H88" s="72"/>
+      <c r="I88" s="72"/>
+      <c r="J88" s="72"/>
+      <c r="K88" s="72"/>
+      <c r="L88" s="72"/>
+      <c r="M88" s="72"/>
+      <c r="N88" s="72"/>
+      <c r="O88" s="72"/>
+      <c r="P88" s="72"/>
+      <c r="Q88" s="72"/>
+      <c r="R88" s="72"/>
+      <c r="S88" s="72"/>
+      <c r="T88" s="72"/>
+      <c r="U88" s="73"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A89" s="64"/>
+      <c r="A89" s="67"/>
       <c r="B89" s="3" t="s">
         <v>131</v>
       </c>
       <c r="C89" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D89" s="82"/>
-      <c r="E89" s="82"/>
-      <c r="F89" s="82"/>
-      <c r="G89" s="82"/>
-      <c r="H89" s="82"/>
-      <c r="I89" s="82"/>
-      <c r="J89" s="82"/>
-      <c r="K89" s="82"/>
-      <c r="L89" s="82"/>
-      <c r="M89" s="82"/>
-      <c r="N89" s="82"/>
-      <c r="O89" s="82"/>
-      <c r="P89" s="82"/>
-      <c r="Q89" s="82"/>
-      <c r="R89" s="82"/>
-      <c r="S89" s="82"/>
-      <c r="T89" s="82"/>
-      <c r="U89" s="83"/>
+      <c r="D89" s="72"/>
+      <c r="E89" s="72"/>
+      <c r="F89" s="72"/>
+      <c r="G89" s="72"/>
+      <c r="H89" s="72"/>
+      <c r="I89" s="72"/>
+      <c r="J89" s="72"/>
+      <c r="K89" s="72"/>
+      <c r="L89" s="72"/>
+      <c r="M89" s="72"/>
+      <c r="N89" s="72"/>
+      <c r="O89" s="72"/>
+      <c r="P89" s="72"/>
+      <c r="Q89" s="72"/>
+      <c r="R89" s="72"/>
+      <c r="S89" s="72"/>
+      <c r="T89" s="72"/>
+      <c r="U89" s="73"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="64"/>
+      <c r="A90" s="67"/>
       <c r="B90" s="3" t="s">
         <v>132</v>
       </c>
       <c r="C90" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D90" s="82"/>
-      <c r="E90" s="82"/>
-      <c r="F90" s="82"/>
-      <c r="G90" s="82"/>
-      <c r="H90" s="82"/>
-      <c r="I90" s="82"/>
-      <c r="J90" s="82"/>
-      <c r="K90" s="82"/>
-      <c r="L90" s="82"/>
-      <c r="M90" s="82"/>
-      <c r="N90" s="82"/>
-      <c r="O90" s="82"/>
-      <c r="P90" s="82"/>
-      <c r="Q90" s="82"/>
-      <c r="R90" s="82"/>
-      <c r="S90" s="82"/>
-      <c r="T90" s="82"/>
-      <c r="U90" s="83"/>
+      <c r="D90" s="72"/>
+      <c r="E90" s="72"/>
+      <c r="F90" s="72"/>
+      <c r="G90" s="72"/>
+      <c r="H90" s="72"/>
+      <c r="I90" s="72"/>
+      <c r="J90" s="72"/>
+      <c r="K90" s="72"/>
+      <c r="L90" s="72"/>
+      <c r="M90" s="72"/>
+      <c r="N90" s="72"/>
+      <c r="O90" s="72"/>
+      <c r="P90" s="72"/>
+      <c r="Q90" s="72"/>
+      <c r="R90" s="72"/>
+      <c r="S90" s="72"/>
+      <c r="T90" s="72"/>
+      <c r="U90" s="73"/>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="64"/>
+      <c r="A91" s="67"/>
       <c r="B91" s="3" t="s">
         <v>133</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D91" s="82"/>
-      <c r="E91" s="82"/>
-      <c r="F91" s="82"/>
-      <c r="G91" s="82"/>
-      <c r="H91" s="82"/>
-      <c r="I91" s="82"/>
-      <c r="J91" s="82"/>
-      <c r="K91" s="82"/>
-      <c r="L91" s="82"/>
-      <c r="M91" s="82"/>
-      <c r="N91" s="82"/>
-      <c r="O91" s="82"/>
-      <c r="P91" s="82"/>
-      <c r="Q91" s="82"/>
-      <c r="R91" s="82"/>
-      <c r="S91" s="82"/>
-      <c r="T91" s="82"/>
-      <c r="U91" s="83"/>
+      <c r="D91" s="72"/>
+      <c r="E91" s="72"/>
+      <c r="F91" s="72"/>
+      <c r="G91" s="72"/>
+      <c r="H91" s="72"/>
+      <c r="I91" s="72"/>
+      <c r="J91" s="72"/>
+      <c r="K91" s="72"/>
+      <c r="L91" s="72"/>
+      <c r="M91" s="72"/>
+      <c r="N91" s="72"/>
+      <c r="O91" s="72"/>
+      <c r="P91" s="72"/>
+      <c r="Q91" s="72"/>
+      <c r="R91" s="72"/>
+      <c r="S91" s="72"/>
+      <c r="T91" s="72"/>
+      <c r="U91" s="73"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A92" s="64"/>
+      <c r="A92" s="67"/>
       <c r="B92" s="3" t="s">
         <v>134</v>
       </c>
       <c r="C92" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D92" s="82"/>
-      <c r="E92" s="82"/>
-      <c r="F92" s="82"/>
-      <c r="G92" s="82"/>
-      <c r="H92" s="82"/>
-      <c r="I92" s="82"/>
-      <c r="J92" s="82"/>
-      <c r="K92" s="82"/>
-      <c r="L92" s="82"/>
-      <c r="M92" s="82"/>
-      <c r="N92" s="82"/>
-      <c r="O92" s="82"/>
-      <c r="P92" s="82"/>
-      <c r="Q92" s="82"/>
-      <c r="R92" s="82"/>
-      <c r="S92" s="82"/>
-      <c r="T92" s="82"/>
-      <c r="U92" s="83"/>
+      <c r="D92" s="72"/>
+      <c r="E92" s="72"/>
+      <c r="F92" s="72"/>
+      <c r="G92" s="72"/>
+      <c r="H92" s="72"/>
+      <c r="I92" s="72"/>
+      <c r="J92" s="72"/>
+      <c r="K92" s="72"/>
+      <c r="L92" s="72"/>
+      <c r="M92" s="72"/>
+      <c r="N92" s="72"/>
+      <c r="O92" s="72"/>
+      <c r="P92" s="72"/>
+      <c r="Q92" s="72"/>
+      <c r="R92" s="72"/>
+      <c r="S92" s="72"/>
+      <c r="T92" s="72"/>
+      <c r="U92" s="73"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A93" s="64"/>
+      <c r="A93" s="67"/>
       <c r="B93" s="3" t="s">
         <v>135</v>
       </c>
       <c r="C93" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D93" s="82"/>
-      <c r="E93" s="82"/>
-      <c r="F93" s="82"/>
-      <c r="G93" s="82"/>
-      <c r="H93" s="82"/>
-      <c r="I93" s="82"/>
-      <c r="J93" s="82"/>
-      <c r="K93" s="82"/>
-      <c r="L93" s="82"/>
-      <c r="M93" s="82"/>
-      <c r="N93" s="82"/>
-      <c r="O93" s="82"/>
-      <c r="P93" s="82"/>
-      <c r="Q93" s="82"/>
-      <c r="R93" s="82"/>
-      <c r="S93" s="82"/>
-      <c r="T93" s="82"/>
-      <c r="U93" s="83"/>
+      <c r="D93" s="72"/>
+      <c r="E93" s="72"/>
+      <c r="F93" s="72"/>
+      <c r="G93" s="72"/>
+      <c r="H93" s="72"/>
+      <c r="I93" s="72"/>
+      <c r="J93" s="72"/>
+      <c r="K93" s="72"/>
+      <c r="L93" s="72"/>
+      <c r="M93" s="72"/>
+      <c r="N93" s="72"/>
+      <c r="O93" s="72"/>
+      <c r="P93" s="72"/>
+      <c r="Q93" s="72"/>
+      <c r="R93" s="72"/>
+      <c r="S93" s="72"/>
+      <c r="T93" s="72"/>
+      <c r="U93" s="73"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A94" s="64"/>
+      <c r="A94" s="67"/>
       <c r="B94" s="3" t="s">
         <v>136</v>
       </c>
       <c r="C94" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D94" s="84"/>
-      <c r="E94" s="84"/>
-      <c r="F94" s="84"/>
-      <c r="G94" s="84"/>
-      <c r="H94" s="84"/>
-      <c r="I94" s="84"/>
-      <c r="J94" s="84"/>
-      <c r="K94" s="84"/>
-      <c r="L94" s="84"/>
-      <c r="M94" s="84"/>
-      <c r="N94" s="84"/>
-      <c r="O94" s="84"/>
-      <c r="P94" s="84"/>
-      <c r="Q94" s="84"/>
-      <c r="R94" s="84"/>
-      <c r="S94" s="84"/>
-      <c r="T94" s="84"/>
-      <c r="U94" s="85"/>
+      <c r="D94" s="75"/>
+      <c r="E94" s="75"/>
+      <c r="F94" s="75"/>
+      <c r="G94" s="75"/>
+      <c r="H94" s="75"/>
+      <c r="I94" s="75"/>
+      <c r="J94" s="75"/>
+      <c r="K94" s="75"/>
+      <c r="L94" s="75"/>
+      <c r="M94" s="75"/>
+      <c r="N94" s="75"/>
+      <c r="O94" s="75"/>
+      <c r="P94" s="75"/>
+      <c r="Q94" s="75"/>
+      <c r="R94" s="75"/>
+      <c r="S94" s="75"/>
+      <c r="T94" s="75"/>
+      <c r="U94" s="76"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="71">
+      <c r="A95" s="63">
         <v>14</v>
       </c>
       <c r="B95" s="12" t="s">
@@ -15227,7 +15227,7 @@
       <c r="U95" s="15"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="71"/>
+      <c r="A96" s="63"/>
       <c r="B96" s="35" t="s">
         <v>139</v>
       </c>
@@ -15258,7 +15258,7 @@
       <c r="U96" s="15"/>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="71"/>
+      <c r="A97" s="63"/>
       <c r="B97" s="35" t="s">
         <v>140</v>
       </c>
@@ -15289,7 +15289,7 @@
       <c r="U97" s="15"/>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="71"/>
+      <c r="A98" s="63"/>
       <c r="B98" s="35" t="s">
         <v>141</v>
       </c>
@@ -15320,7 +15320,7 @@
       <c r="U98" s="15"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="71"/>
+      <c r="A99" s="63"/>
       <c r="B99" s="35" t="s">
         <v>142</v>
       </c>
@@ -15351,7 +15351,7 @@
       <c r="U99" s="15"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="71"/>
+      <c r="A100" s="63"/>
       <c r="B100" s="35" t="s">
         <v>143</v>
       </c>
@@ -15382,7 +15382,7 @@
       <c r="U100" s="15"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="71"/>
+      <c r="A101" s="63"/>
       <c r="B101" s="35" t="s">
         <v>144</v>
       </c>
@@ -15413,7 +15413,7 @@
       <c r="U101" s="15"/>
     </row>
     <row r="102" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="64">
+      <c r="A102" s="67">
         <v>15</v>
       </c>
       <c r="B102" s="39" t="s">
@@ -15446,7 +15446,7 @@
       <c r="U102" s="6"/>
     </row>
     <row r="103" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="64"/>
+      <c r="A103" s="67"/>
       <c r="B103" s="39" t="s">
         <v>146</v>
       </c>
@@ -15477,7 +15477,7 @@
       <c r="U103" s="6"/>
     </row>
     <row r="104" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="64"/>
+      <c r="A104" s="67"/>
       <c r="B104" s="39" t="s">
         <v>147</v>
       </c>
@@ -15508,7 +15508,7 @@
       <c r="U104" s="6"/>
     </row>
     <row r="105" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="64"/>
+      <c r="A105" s="67"/>
       <c r="B105" s="39" t="s">
         <v>148</v>
       </c>
@@ -15539,7 +15539,7 @@
       <c r="U105" s="6"/>
     </row>
     <row r="106" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="64"/>
+      <c r="A106" s="67"/>
       <c r="B106" s="39" t="s">
         <v>149</v>
       </c>
@@ -15570,7 +15570,7 @@
       <c r="U106" s="6"/>
     </row>
     <row r="107" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="64"/>
+      <c r="A107" s="67"/>
       <c r="B107" s="39" t="s">
         <v>150</v>
       </c>
@@ -15601,7 +15601,7 @@
       <c r="U107" s="6"/>
     </row>
     <row r="108" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="64"/>
+      <c r="A108" s="67"/>
       <c r="B108" s="39" t="s">
         <v>151</v>
       </c>
@@ -15632,7 +15632,7 @@
       <c r="U108" s="6"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="71">
+      <c r="A109" s="63">
         <v>16</v>
       </c>
       <c r="B109" s="35" t="s">
@@ -15665,7 +15665,7 @@
       <c r="U109" s="14"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="71"/>
+      <c r="A110" s="63"/>
       <c r="B110" s="35" t="s">
         <v>153</v>
       </c>
@@ -15696,7 +15696,7 @@
       <c r="U110" s="14"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="71"/>
+      <c r="A111" s="63"/>
       <c r="B111" s="35" t="s">
         <v>154</v>
       </c>
@@ -15727,7 +15727,7 @@
       <c r="U111" s="14"/>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="71"/>
+      <c r="A112" s="63"/>
       <c r="B112" s="35" t="s">
         <v>155</v>
       </c>
@@ -15758,7 +15758,7 @@
       <c r="U112" s="14"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="71"/>
+      <c r="A113" s="63"/>
       <c r="B113" s="35" t="s">
         <v>156</v>
       </c>
@@ -15789,7 +15789,7 @@
       <c r="U113" s="14"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="71"/>
+      <c r="A114" s="63"/>
       <c r="B114" s="35" t="s">
         <v>157</v>
       </c>
@@ -15820,7 +15820,7 @@
       <c r="U114" s="14"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="71"/>
+      <c r="A115" s="63"/>
       <c r="B115" s="35" t="s">
         <v>158</v>
       </c>
@@ -15851,7 +15851,7 @@
       <c r="U115" s="14"/>
     </row>
     <row r="116" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A116" s="64">
+      <c r="A116" s="67">
         <v>17</v>
       </c>
       <c r="B116" s="39" t="s">
@@ -15884,7 +15884,7 @@
       <c r="U116" s="6"/>
     </row>
     <row r="117" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A117" s="64"/>
+      <c r="A117" s="67"/>
       <c r="B117" s="39" t="s">
         <v>160</v>
       </c>
@@ -15915,7 +15915,7 @@
       <c r="U117" s="6"/>
     </row>
     <row r="118" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="64"/>
+      <c r="A118" s="67"/>
       <c r="B118" s="39" t="s">
         <v>161</v>
       </c>
@@ -15946,7 +15946,7 @@
       <c r="U118" s="6"/>
     </row>
     <row r="119" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="64"/>
+      <c r="A119" s="67"/>
       <c r="B119" s="39" t="s">
         <v>162</v>
       </c>
@@ -15977,7 +15977,7 @@
       <c r="U119" s="6"/>
     </row>
     <row r="120" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="64"/>
+      <c r="A120" s="67"/>
       <c r="B120" s="39" t="s">
         <v>163</v>
       </c>
@@ -16008,7 +16008,7 @@
       <c r="U120" s="6"/>
     </row>
     <row r="121" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="64"/>
+      <c r="A121" s="67"/>
       <c r="B121" s="39" t="s">
         <v>164</v>
       </c>
@@ -16039,7 +16039,7 @@
       <c r="U121" s="6"/>
     </row>
     <row r="122" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="64"/>
+      <c r="A122" s="67"/>
       <c r="B122" s="39" t="s">
         <v>165</v>
       </c>
@@ -16070,7 +16070,7 @@
       <c r="U122" s="6"/>
     </row>
     <row r="123" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="71">
+      <c r="A123" s="63">
         <v>18</v>
       </c>
       <c r="B123" s="35" t="s">
@@ -16103,7 +16103,7 @@
       <c r="U123" s="14"/>
     </row>
     <row r="124" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="71"/>
+      <c r="A124" s="63"/>
       <c r="B124" s="35" t="s">
         <v>167</v>
       </c>
@@ -16134,7 +16134,7 @@
       <c r="U124" s="14"/>
     </row>
     <row r="125" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="71"/>
+      <c r="A125" s="63"/>
       <c r="B125" s="35" t="s">
         <v>168</v>
       </c>
@@ -16165,7 +16165,7 @@
       <c r="U125" s="14"/>
     </row>
     <row r="126" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="71"/>
+      <c r="A126" s="63"/>
       <c r="B126" s="35" t="s">
         <v>169</v>
       </c>
@@ -16196,36 +16196,36 @@
       <c r="U126" s="14"/>
     </row>
     <row r="127" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="71"/>
+      <c r="A127" s="63"/>
       <c r="B127" s="34" t="s">
         <v>170</v>
       </c>
       <c r="C127" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="D127" s="77" t="s">
+      <c r="D127" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="E127" s="78"/>
-      <c r="F127" s="78"/>
-      <c r="G127" s="78"/>
-      <c r="H127" s="78"/>
-      <c r="I127" s="78"/>
-      <c r="J127" s="78"/>
-      <c r="K127" s="78"/>
-      <c r="L127" s="78"/>
-      <c r="M127" s="78"/>
-      <c r="N127" s="78"/>
-      <c r="O127" s="78"/>
-      <c r="P127" s="78"/>
-      <c r="Q127" s="78"/>
-      <c r="R127" s="78"/>
-      <c r="S127" s="78"/>
-      <c r="T127" s="78"/>
-      <c r="U127" s="79"/>
+      <c r="E127" s="65"/>
+      <c r="F127" s="65"/>
+      <c r="G127" s="65"/>
+      <c r="H127" s="65"/>
+      <c r="I127" s="65"/>
+      <c r="J127" s="65"/>
+      <c r="K127" s="65"/>
+      <c r="L127" s="65"/>
+      <c r="M127" s="65"/>
+      <c r="N127" s="65"/>
+      <c r="O127" s="65"/>
+      <c r="P127" s="65"/>
+      <c r="Q127" s="65"/>
+      <c r="R127" s="65"/>
+      <c r="S127" s="65"/>
+      <c r="T127" s="65"/>
+      <c r="U127" s="66"/>
     </row>
     <row r="128" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="71"/>
+      <c r="A128" s="63"/>
       <c r="B128" s="35" t="s">
         <v>171</v>
       </c>
@@ -16256,7 +16256,7 @@
       <c r="U128" s="14"/>
     </row>
     <row r="129" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="71"/>
+      <c r="A129" s="63"/>
       <c r="B129" s="35" t="s">
         <v>172</v>
       </c>
@@ -16287,7 +16287,7 @@
       <c r="U129" s="14"/>
     </row>
     <row r="130" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A130" s="64">
+      <c r="A130" s="67">
         <v>19</v>
       </c>
       <c r="B130" s="39" t="s">
@@ -16320,7 +16320,7 @@
       <c r="U130" s="6"/>
     </row>
     <row r="131" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A131" s="64"/>
+      <c r="A131" s="67"/>
       <c r="B131" s="39" t="s">
         <v>174</v>
       </c>
@@ -16351,7 +16351,7 @@
       <c r="U131" s="6"/>
     </row>
     <row r="132" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A132" s="64"/>
+      <c r="A132" s="67"/>
       <c r="B132" s="39" t="s">
         <v>175</v>
       </c>
@@ -16382,7 +16382,7 @@
       <c r="U132" s="6"/>
     </row>
     <row r="133" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A133" s="64"/>
+      <c r="A133" s="67"/>
       <c r="B133" s="39" t="s">
         <v>176</v>
       </c>
@@ -16413,7 +16413,7 @@
       <c r="U133" s="6"/>
     </row>
     <row r="134" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A134" s="64"/>
+      <c r="A134" s="67"/>
       <c r="B134" s="39" t="s">
         <v>177</v>
       </c>
@@ -16444,7 +16444,7 @@
       <c r="U134" s="6"/>
     </row>
     <row r="135" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A135" s="64"/>
+      <c r="A135" s="67"/>
       <c r="B135" s="39" t="s">
         <v>178</v>
       </c>
@@ -16475,7 +16475,7 @@
       <c r="U135" s="6"/>
     </row>
     <row r="136" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A136" s="64"/>
+      <c r="A136" s="67"/>
       <c r="B136" s="39" t="s">
         <v>179</v>
       </c>
@@ -16521,28 +16521,6 @@
     <row r="150" ht="20.25"/>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A123:A129"/>
-    <mergeCell ref="D127:U127"/>
-    <mergeCell ref="A130:A136"/>
-    <mergeCell ref="D81:U94"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A102:A108"/>
-    <mergeCell ref="A109:A115"/>
-    <mergeCell ref="A116:A122"/>
-    <mergeCell ref="A81:A87"/>
-    <mergeCell ref="A46:A52"/>
-    <mergeCell ref="A53:A59"/>
-    <mergeCell ref="A60:A66"/>
-    <mergeCell ref="A67:A73"/>
-    <mergeCell ref="A74:A80"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="D29:U31"/>
-    <mergeCell ref="M2:O2"/>
     <mergeCell ref="A32:A38"/>
     <mergeCell ref="D35:U41"/>
     <mergeCell ref="A39:A45"/>
@@ -16558,6 +16536,28 @@
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="D29:U31"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="A46:A52"/>
+    <mergeCell ref="A53:A59"/>
+    <mergeCell ref="A60:A66"/>
+    <mergeCell ref="A67:A73"/>
+    <mergeCell ref="A74:A80"/>
+    <mergeCell ref="A123:A129"/>
+    <mergeCell ref="D127:U127"/>
+    <mergeCell ref="A130:A136"/>
+    <mergeCell ref="D81:U94"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="A95:A101"/>
+    <mergeCell ref="A102:A108"/>
+    <mergeCell ref="A109:A115"/>
+    <mergeCell ref="A116:A122"/>
+    <mergeCell ref="A81:A87"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
